--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7704783.552449092</v>
+        <v>7541536.325806242</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7788259.071153432</v>
+        <v>7625011.844510582</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7704783.552449092</v>
+        <v>7541536.325806242</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2508085.008740827</v>
+        <v>-2671332.235383678</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7704783.552449092</v>
+        <v>-7541536.325806242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-4730827.555403571</v>
+        <v>-4567580.328760721</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:10:17+00:00</t>
+          <t>2026-06-08T14:49:57+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1969148.374877319</v>
+        <v>2456919.680106931</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1969148.374877319</v>
+        <v>2456919.680106931</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-1969148.374877319</v>
+        <v>-2456919.680106931</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -922,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1082260.433733041</v>
+        <v>1350343.627003441</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1082260.433733041</v>
+        <v>1350343.627003441</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1577558.566266959</v>
+        <v>1309475.372996559</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -941,12 +943,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -956,44 +958,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>387977397.421864</v>
+        <v>334974961.947338</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>867900893.337617</v>
+        <v>282411706.537503</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>479923495.915753</v>
+        <v>-52563255.409835</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-1295372.434767436</v>
+        <v>575230.6970620001</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-1295372.434767436</v>
+        <v>575230.6970620001</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>387977397.421864</v>
+        <v>333260817.2342123</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>794154.7458686491</v>
+        <v>851129.1854138965</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>794154.7458686491</v>
+        <v>851129.1854138965</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-2089527.180636085</v>
+        <v>-275898.4883518965</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1006,12 +1008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,58 +1027,62 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>334974961.947338</v>
+        <v>275418608.32134</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>282411706.537503</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-52563255.409835</v>
+        <v>-124665800.7959487</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>575230.6970620001</v>
+        <v>604546.7198706791</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>575230.6970620001</v>
+        <v>604546.7198706791</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>333260817.2342123</v>
+        <v>232362954.9288507</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>682154.8404038538</v>
+        <v>593441.7798956764</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>682154.8404038538</v>
+        <v>593441.7798956764</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-106924.1433418538</v>
+        <v>11104.93997500272</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0</v>
+        <v>39014674.44036614</v>
       </c>
       <c r="R5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1086,131 +1092,131 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>246097994.8466104</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>252839704.1525801</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>168999271.92389</v>
+        <v>6741709.305969649</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-1212564.103655469</v>
+        <v>570329.5748531731</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-1212564.103655469</v>
+        <v>570329.5748531731</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>170360077.113777</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>589061.4086461823</v>
+        <v>435089.9540613988</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>589061.4086461823</v>
+        <v>435089.9540613988</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-1801625.512301651</v>
+        <v>135239.6207917743</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>75936994.49835326</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>275418608.32134</v>
+        <v>196856311.4279603</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-124665800.7959487</v>
+        <v>-53957591.71043837</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>604546.7198706791</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>604546.7198706791</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>232362954.9288507</v>
+        <v>151191144.4963191</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>475626.0149355049</v>
+        <v>386133.589675829</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>475626.0149355049</v>
+        <v>347668.4253677963</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>128920.7049351742</v>
+        <v>-386133.589675829</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>39014674.44036614</v>
+        <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>38465.16430803272</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1220,113 +1226,109 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>246097994.8466104</v>
+        <v>200002600.606636</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>252839704.1525801</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>6741709.305969649</v>
+        <v>-100000441.3465193</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>570329.5748531731</v>
+        <v>415095.0057011207</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>570329.5748531731</v>
+        <v>415095.0057011207</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>170360077.113777</v>
+        <v>109444257.5753876</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>348711.7152841411</v>
+        <v>279514.4132798024</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>348711.7152841411</v>
+        <v>279514.4132798024</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>221617.859569032</v>
+        <v>135580.5924213182</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>75936994.49835326</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>152857139.195815</v>
+        <v>100000617.7417743</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-79237170.953592</v>
+        <v>-163.2954034076501</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-421343.6247346211</v>
+        <v>9382.718447380783</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-421343.6247346211</v>
+        <v>9382.718447380783</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>152857139.195815</v>
+        <v>100000309.8058436</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>312884.7797292335</v>
+        <v>255395.1074493354</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>312884.7797292335</v>
+        <v>255395.1074493354</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-734228.4044638546</v>
+        <v>-246012.3890019546</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1339,82 +1341,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>196856311.4279603</v>
+        <v>100000062.958447</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>100000230.666889</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-53957591.71043837</v>
+        <v>167.708442</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0</v>
+        <v>71459.446648</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>71459.446648</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>151191144.4963191</v>
+        <v>99997763.22495648</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>309474.6388138386</v>
+        <v>255388.6036264916</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>271009.4745058059</v>
+        <v>255388.6036264916</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-309474.6388138386</v>
+        <v>-183929.1569784916</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>38465.16430803272</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1423,123 +1425,123 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>200002600.606636</v>
+        <v>101411572.6019855</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-100000441.3465193</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>415095.0057011207</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>415095.0057011207</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>109444257.5753876</v>
+        <v>101411572.6019855</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>224022.5258974503</v>
+        <v>258999.392417649</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>224022.5258974503</v>
+        <v>233198.8548539802</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>191072.4798036703</v>
+        <v>-258999.392417649</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>25800.53756366883</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>100000617.7417743</v>
+        <v>75305516.51778577</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-163.2954034076501</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>9382.718447380783</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>9382.718447380783</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>100000309.8058436</v>
+        <v>75305516.51778577</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>204691.6164404647</v>
+        <v>192326.0089886613</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>204691.6164404647</v>
+        <v>173167.2211125075</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-195308.897993084</v>
+        <v>-192326.0089886613</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
+        <v>19158.78787615384</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1549,44 +1551,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>100000062.958447</v>
+        <v>55000541.20928549</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>167.708442</v>
+        <v>45001420.37224875</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>71459.446648</v>
+        <v>172403.0735875274</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>71459.446648</v>
+        <v>172403.0735875274</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>99997763.22495648</v>
+        <v>54328358.31940126</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>204686.4038190319</v>
+        <v>138751.5392449181</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>204686.4038190319</v>
+        <v>138751.5392449181</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-133226.9571710319</v>
+        <v>33651.53434260924</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1599,32 +1601,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>101411572.6019855</v>
+        <v>47958113.065451</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>37220.756204</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>323394.9088048668</v>
+        <v>-47920892.309247</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
@@ -1639,57 +1641,49 @@
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>101411572.6019855</v>
+        <v>46412277.82966884</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>207580.3441206632</v>
+        <v>118534.319606518</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>181779.8065569944</v>
+        <v>118534.319606518</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-207580.3441206632</v>
+        <v>-118534.319606518</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>25800.53756366883</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" s="6" t="n">
-        <v>75305516.51778577</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>240144.3939968634</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1704,37 +1698,41 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>75305516.51778577</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>154143.6014832119</v>
+        <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>134984.8136070581</v>
+        <v>-96797.73390613489</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-154143.6014832119</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>19158.78787615384</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
+        <v>96797.73390613489</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1744,74 +1742,86 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>55000541.20928549</v>
+        <v>50000340.64647674</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>45001420.37224875</v>
+        <v>539.2093880709065</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>172403.0735875274</v>
+        <v>83475.51870433975</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>172403.0735875274</v>
+        <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>83475.51870433975</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>54328358.31940126</v>
+        <v>49997665.28166009</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>111205.2503091863</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>111205.2503091863</v>
+        <v>83475.51870433975</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>61197.82327834109</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0</v>
+        <v>49997665.28166009</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>Aave Ethereum USDT (aToken)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>495610843.871423</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>495610843.871423</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>0</v>
@@ -1826,41 +1836,37 @@
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0</v>
+        <v>15987446.57649752</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>40831.02986553439</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>-96797.73390613489</v>
+        <v>40831.02986553439</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0</v>
+        <v>-40831.02986553439</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>96797.73390613489</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1870,44 +1876,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>47958113.065451</v>
+        <v>10113369.18090356</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>37220.756204</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-47920892.309247</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>46412277.82966884</v>
+        <v>10113369.18090356</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>95001.7473954236</v>
+        <v>25828.970066658</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>95001.7473954236</v>
+        <v>25828.970066658</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-95001.7473954236</v>
+        <v>17711.94226062157</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1920,128 +1926,124 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>50000340.64647674</v>
+        <v>10000143.505486</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>10000122.636328</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>539.2093880709065</v>
+        <v>-20.869158</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>19310.411142</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>19310.411142</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>49997665.28166009</v>
+        <v>9999519.915798903</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>25538.20551451926</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>25538.20551451926</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0</v>
+        <v>-6227.79437251926</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>49997665.28166009</v>
+        <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>4997665.827264</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>4987120.646667</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>-10545.180597</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0</v>
+        <v>3.225e-11</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0</v>
+        <v>3.225e-11</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>15987446.57649752</v>
+        <v>4999233.117450742</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>32724.86144145544</v>
+        <v>12767.75723669806</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>32724.86144145544</v>
+        <v>12767.75723669806</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-32724.86144145544</v>
+        <v>-12767.75723669803</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2056,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>10113369.18090356</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>3.218e-09</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>3.218e-09</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>10113369.18090356</v>
+        <v>4991412.147209223</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>20701.15471959626</v>
+        <v>12747.78292322775</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>20701.15471959626</v>
+        <v>12747.78292322775</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>22839.75760768331</v>
+        <v>-12747.78292322453</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,59 +2121,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10000143.505486</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>4997775.722557</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-20.869158</v>
+        <v>-2224.277443</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>19310.411142</v>
+        <v>1.3225e-09</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>19310.411142</v>
+        <v>1.3225e-09</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>9999519.915798903</v>
+        <v>4983312.81205645</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>20468.11554051694</v>
+        <v>12727.09768159573</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>20468.11554051694</v>
+        <v>12727.09768159573</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-1157.704398516946</v>
+        <v>-12727.0976815944</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,17 +2186,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2203,40 +2205,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>4983790.597531</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>4442753.639281</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-10545.180597</v>
+        <v>-541036.95825</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>-1.663e-08</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>-1.663e-08</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4999233.117450742</v>
+        <v>4975726.070058748</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10232.97937536888</v>
+        <v>12707.72157374711</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>10232.97937536888</v>
+        <v>12707.72157374711</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-10232.97937536884</v>
+        <v>-12707.72157376374</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,59 +2251,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5000000</v>
+        <v>977613.8365042645</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5000000</v>
+        <v>977119.890305955</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0</v>
+        <v>-493.9461983095568</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>4849.497356413308</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>4849.497356413308</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4991412.147209223</v>
+        <v>1717843.021793645</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>10216.97055455645</v>
+        <v>4387.273439291298</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>10216.97055455645</v>
+        <v>4387.273439291298</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-10216.97055455323</v>
+        <v>462.2239171220098</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2314,124 +2316,124 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5000000</v>
+        <v>976348.3873033939</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-2224.277443</v>
+        <v>3113.511501423833</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4983312.81205645</v>
+        <v>976348.3873033939</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>10200.3919458728</v>
+        <v>2493.538287706028</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>10200.3919458728</v>
+        <v>2245.141456895463</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-10200.39194587148</v>
+        <v>-2493.538287706028</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0</v>
+        <v>248.3968308105648</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4983790.597531</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-541036.95825</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>3.480000000005129</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>3.480000000005129</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4975726.070058748</v>
+        <v>2580.581437997849</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>10184.86256915346</v>
+        <v>6.590658318147608</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>10184.86256915346</v>
+        <v>6.590658318147608</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-10184.86256917009</v>
+        <v>-3.110658318142479</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,17 +2446,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2463,40 +2465,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>977613.8365042645</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>977119.890305955</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-493.9461983095568</v>
+        <v>-66.81783951655405</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>4849.497356413308</v>
+        <v>1.29454480160933</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>4849.497356413308</v>
+        <v>1.29454480160933</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>1717843.021793645</v>
+        <v>458.062434320099</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>3516.269755609956</v>
+        <v>1.169865422005418</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>3516.269755609956</v>
+        <v>1.169865422005418</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>1333.227600803353</v>
+        <v>0.1246793796039116</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2509,17 +2511,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2528,105 +2530,105 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>976348.3873033939</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3113.511501423833</v>
+        <v>15.02635028417003</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>976348.3873033939</v>
+        <v>345.4148236875836</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1998.497104600911</v>
+        <v>0.8821698270891616</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1750.100273790347</v>
+        <v>0.8821698270891616</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-1998.497104600911</v>
+        <v>0.07126668266949587</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>248.3968308105648</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>94443.720094</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>504861.558051</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>410417.837957</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-1245.293808066253</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-1245.293808066253</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>94443.720094</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>193.3177783771424</v>
+        <v>0.7250574374868018</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>193.3177783771424</v>
+        <v>0.7250574374868018</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-1438.611586443395</v>
+        <v>-0.7250574374868018</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2639,59 +2641,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>10.263802</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>10.263802</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3.480000000005129</v>
+        <v>-2.0038e-09</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>3.480000000005129</v>
+        <v>-2.0038e-09</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>2580.581437997849</v>
+        <v>220.7452180964028</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>5.282217494381915</v>
+        <v>0.5637707403518795</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>5.282217494381915</v>
+        <v>0.5637707403518795</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-1.802217494376787</v>
+        <v>-0.5637707423556795</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2704,17 +2706,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2723,40 +2725,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-66.81783951655405</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1.29454480160933</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1.29454480160933</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>458.062434320099</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.9376124963380483</v>
+        <v>0.2525372615423412</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.9376124963380483</v>
+        <v>0.2525372615423412</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.3569323052712814</v>
+        <v>0.03606051573508011</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,12 +2771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2784,44 +2786,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>1868.74164</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>15.02635028417003</v>
+        <v>-1868.74164</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>-5.583040730011e-08</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>-5.583040730011e-08</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>345.4148236875836</v>
+        <v>49.19685112472924</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.7070329956015594</v>
+        <v>0.1256459615331607</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.7070329956015594</v>
+        <v>0.1256459615331607</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.246403514157098</v>
+        <v>-0.125646017363568</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,17 +2836,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2853,40 +2855,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.5811120673907055</v>
+        <v>0.05594819789455457</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5811120673907055</v>
+        <v>0.05594819789455457</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.5811120673907055</v>
+        <v>-0.05594214568810445</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,59 +2901,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0</v>
+        <v>1.210594</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>10.263802</v>
+        <v>133501.211399</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>10.263802</v>
+        <v>133500.000805</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-2.0038e-09</v>
+        <v>133500.000805</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-2.0038e-09</v>
+        <v>133500.000805</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>220.7452180964028</v>
+        <v>1.210594</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.4518455552926217</v>
+        <v>0.003091788268534479</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4518455552926217</v>
+        <v>0.003091788268534479</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.4518455572964217</v>
+        <v>133499.9977132117</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,12 +2966,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2979,44 +2981,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>0.057463</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0.05756</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>9.7e-05</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>9.7e-05</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>9.7e-05</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>0.057463</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2024011375660545</v>
+        <v>0.0001467572359311187</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2024011375660545</v>
+        <v>0.0001467572359311187</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.08619663971136672</v>
+        <v>-4.975723593111874e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,59 +3031,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1868.74164</v>
+        <v>0.006319</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0</v>
+        <v>0.006327</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-1868.74164</v>
+        <v>8e-06</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-5.583040730011e-08</v>
+        <v>8e-06</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-5.583040730011e-08</v>
+        <v>8e-06</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>49.19685112472924</v>
+        <v>0.006319</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1007015178258304</v>
+        <v>1.613836684211996e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.1007015178258304</v>
+        <v>1.613836684211996e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-0.1007015736562377</v>
+        <v>-8.13836684211996e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,12 +3096,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3109,44 +3111,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.04484082400145126</v>
+        <v>1.466141220037101e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.04484082400145126</v>
+        <v>1.466141220037101e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.04483477179500113</v>
+        <v>-1.418112848132801e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,59 +3161,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1.210594</v>
+        <v>0.001692</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>133501.211399</v>
+        <v>0.001696</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>133500.000805</v>
+        <v>4e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>133500.000805</v>
+        <v>4e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>133500.000805</v>
+        <v>4e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>1.210594</v>
+        <v>0.001692</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.002477976750214504</v>
+        <v>4.321271830490105e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.002477976750214504</v>
+        <v>4.321271830490105e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>133499.9983270233</v>
+        <v>-3.21271830490105e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,12 +3226,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3239,44 +3241,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.057463</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.05756</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.057463</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.0001176215791566586</v>
+        <v>3.167259001422607e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.0001176215791566586</v>
+        <v>3.167259001422607e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.062157915665864e-05</v>
+        <v>-3.167259001422607e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,17 +3291,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3308,40 +3310,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.006319</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.006327</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>8e-06</v>
+        <v>9.12781293076e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>8e-06</v>
+        <v>9.12781293075e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>8e-06</v>
+        <v>9.12781293075e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.006319</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.293442317127414e-05</v>
+        <v>1.326123057409306e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.293442317127414e-05</v>
+        <v>1.326123057409306e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.934423171274141e-06</v>
+        <v>-4.133417643343059e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,12 +3356,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3369,44 +3371,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.175068775814053e-05</v>
+        <v>1.912808317055503e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.175068775814053e-05</v>
+        <v>1.912808317055503e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.127040403909754e-05</v>
+        <v>-1.912808317055503e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,59 +3421,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.001692</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.001696</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.001692</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.463371420445616e-06</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.463371420445616e-06</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>5.366285795543841e-07</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,12 +3486,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3499,14 +3501,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3524,19 +3526,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>2.538464307956313e-06</v>
+        <v>0</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>2.538464307956313e-06</v>
+        <v>0</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-2.538464307956313e-06</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,44 +3566,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>9.12781293076e-07</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.062848364367868e-06</v>
+        <v>0</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.062848364367868e-06</v>
+        <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.500670712928679e-07</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3609,17 +3611,21 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3629,14 +3635,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -3654,19 +3660,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>1.533059228382156e-07</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.533059228382156e-07</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-1.533059228382156e-07</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3679,12 +3685,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3694,7 +3700,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3707,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>805478.9999998595</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>805478.9999998595</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3731,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0</v>
+        <v>805478.9999998595</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3744,12 +3750,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3759,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3772,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>1.16184e-08</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>1.16184e-08</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3796,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>1.16184e-08</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3809,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3824,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3837,13 +3843,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>6.37405e-09</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>6.37405e-09</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>6.37405e-09</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3871,36 +3877,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3918,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3933,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3971,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -3995,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4008,17 +4018,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4027,31 +4037,31 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4060,30 +4070,34 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4092,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4125,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4142,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4161,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4182,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4197,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4211,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>287780830.420175</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>168999271.92389</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-1212564.103655469</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-1212564.103655469</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>287780830.420175</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4263,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-1212564.103655469</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4271,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>387977397.421864</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>867900893.337617</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>479923495.915753</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-1295372.434767436</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-1295372.434767436</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>387977397.421864</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4328,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-1295372.434767436</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>94443.720094</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>504861.558051</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>410417.837957</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-1245.293808066253</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-1245.293808066253</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>94443.720094</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4397,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-1245.293808066253</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>152857139.195815</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>-79237170.953592</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-421343.6247346211</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-421343.6247346211</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>152857139.195815</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4466,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-421343.6247346211</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7704783.552449092</v>
+        <v>7541536.325806242</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7788259.071153432</v>
+        <v>7625011.844510582</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7704783.552449092</v>
+        <v>7541536.325806242</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2508085.008740827</v>
+        <v>-2671332.235383678</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4955,1669 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3131305694.853109</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>105883906.3657945</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>68336335.76099491</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>46518715.05860327</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>159029980.3263338</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2416566757.341383</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>279518.4082718074</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>362190.5254546798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3169303197.190613</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>105819063.6808732</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>61915033.21617521</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>55094509.141181</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>168986345.7344508</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2442518245.417933</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>282520.1538753192</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>366585.6042744216</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3146326464.579185</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>106380840.4381838</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>62816547.65419868</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>42689471.90948798</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>168969242.5220673</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2430500362.055247</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>281130.0744917768</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>363927.9414114685</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2881318553.009124</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>106454430.4482588</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>53142917.37872301</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>55911480.50712221</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>115233339.1487748</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2215606385.526245</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>256273.8100893528</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>333275.1198428256</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2807089586.432195</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>106526378.8617726</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>57673772.47965179</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>49361724.53585335</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>106666507.8312684</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2151891202.723649</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>248904.0296247227</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>324689.2355413834</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2780827269.760019</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>106682515.9973453</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>69545120.86060463</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>46486748.67527746</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>106913226.5360041</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2116229657.690788</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>244779.1453136163</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>321651.5371490523</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2788088641.022816</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>107681253.2199611</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>73529249.4886039</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>46912421.31784251</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>106954288.9193721</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2118041428.077036</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>244988.7083943712</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>322491.4423290278</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2779945566.177685</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>107010807.4831251</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>75438252.07703087</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>44344179.96811678</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>106935113.0757522</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2111247213.57366</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>244202.8381022836</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>321549.5526368708</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2792788068.209374</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>107600220.1741485</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>58260508.43635895</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>48340039.58074408</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>107322066.296092</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2136295233.72203</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>233012.1776308807</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>304617.8351955642</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2792926035.615368</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>107794492.5793762</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>58215579.70095983</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>45805751.94094924</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>107333348.9757696</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2138806862.418313</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>233286.128563637</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>304632.8837175125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2790054498.466092</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>107856454.6880254</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>56297150.14197122</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>35005366.32205565</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>107387902.5867912</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2148537624.727249</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>234347.4922177903</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>304319.676482043</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2787622121.342249</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>107835026.8157272</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>58937195.19455917</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>48424749.6596028</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>106417723.4543805</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2131037426.217979</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>232438.6926758314</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>304054.3697578133</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2791260263.036477</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>107856890.2413078</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>53758642.74291529</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>43642467.25609321</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>106551417.0948813</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2144480845.701279</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>233905.0070686935</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>304451.1928678967</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2802908640.567328</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>107952777.8445753</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>54628413.79015067</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45214622.45488715</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>106911070.5772904</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2153231755.900424</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>234859.4952918416</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>305721.7166098803</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2809376592.82677</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>108076031.9837475</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>54000493.30115246</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>45329448.55387111</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>106936208.3821319</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2160064410.605867</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>235604.7535907805</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>306427.1957107999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2819847342.704478</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>108275019.6506317</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>57421435.15917984</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>42079222.01166449</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>107032449.9192543</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2170069215.963748</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>236696.0079485179</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>307569.2720455311</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>2820880505.400382</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>108480824.027681</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>52467553.34594446</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>46320240.07094195</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>107504855.7115974</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2171137032.244217</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>236812.4778974718</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>307681.9622232834</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2907124641.609815</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>108579051.0268968</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>56498201.94699442</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>40663062.32367405</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>107436888.0729907</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2258977438.239259</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>246393.4964579188</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>317088.8708138351</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2905429817.13824</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>108377058.0866341</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>61287940.00011939</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>46108021.12238023</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>107184053.179774</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2247502744.749332</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>245141.9169592012</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>316904.0111864812</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>2914194882.912043</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>108287715.446821</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>84447370.91364799</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>56111545.25512103</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>107194547.5382319</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2223183703.758221</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>242489.3656592759</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>317860.0434009393</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3077529531.212519</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>108621267.8684392</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>83886845.5979041</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>64911091.2139782</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>107211163.3616333</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2377929163.170564</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>259367.9206019552</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>335675.447134607</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>3137611584.903619</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>108663588.8738396</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>82897801.95004173</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>53511159.10691563</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>107220548.4053871</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2450348486.567435</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>267266.9150765436</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>342228.7783156662</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>3132475429.811056</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>108701902.6320863</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>86422512.14540139</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>46634275.54346722</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>107244908.9822976</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2448501830.507803</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>267065.4947190023</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>341668.562356806</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3117051456.181883</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>108751046.811058</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>87890264.99936663</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>49715414.4930896</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>108592021.8578287</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2427132708.02054</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>264734.6999457804</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>339986.2229374585</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3099592040.943802</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>108755446.1169963</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>86014890.37784478</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>48444881.26366401</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>107978396.0840361</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>2413428427.101261</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>263239.932607699</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>338081.8717501467</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3117529667.747241</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>108967111.5345911</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>88895924.8823521</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>46568078.51505661</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>112655549.2029514</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>2425473003.61229</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>264553.6709698761</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>340038.3829181828</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3113281481.525022</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>109093717.1373149</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>89669597.74944127</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>46803310.00659268</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>112685017.5580367</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>2420059839.073637</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>263963.2407535299</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>339575.0204077042</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3098756108.186975</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>109074883.3027603</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>89370219.19929697</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>47903347.44613171</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>112893900.0040528</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2404543758.234733</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>262270.854922443</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>337990.6940379342</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3242110616.116458</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>109092111.8168385</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>89530342.68923661</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>49134306.49835142</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>112902235.561008</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2546481619.551023</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>277752.4464325994</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>353626.8034756986</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3277107093.689361</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>109138294.8517408</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>89401613.70311053</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>62089606.40613436</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>123415130.4064669</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>2558092448.321908</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>279018.8746178506</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>357443.9750538352</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>3381796950.610221</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>109145503.3638819</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>89546424.48277703</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>75335921.8580665</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>125802289.7933941</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>2646996811.112102</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>288715.9421615233</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>368862.8141505707</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="n">
+        <v>7885254.172933893</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>10212868.56118992</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:49:57+00:00</t>
+          <t>2026-06-08T17:08:48+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4226,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>168999271.92389</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-1212564.103655469</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-1212564.103655469</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-1212564.103655469</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4280,173 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>387977397.421864</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>479923495.915753</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-1295372.434767436</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-1295372.434767436</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>387977397.421864</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-1295372.434767436</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>94443.720094</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>504861.558051</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>410417.837957</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-1245.293808066253</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-1245.293808066253</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>94443.720094</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-1245.293808066253</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>152857139.195815</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>73619968.24222299</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>-79237170.953592</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-421343.6247346211</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-421343.6247346211</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>152857139.195815</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-421343.6247346211</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>287780830.420175</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>456780102.344065</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>387977397.421864</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>94443.720094</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>152857139.195815</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>73619968.24222299</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-2930525.456965593</v>
       </c>
     </row>
   </sheetData>
@@ -4664,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4991,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6610,10 +6500,10 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="11" t="n">
         <v>7885254.172933893</v>
       </c>
-      <c r="O38" s="10" t="n">
+      <c r="O38" s="11" t="n">
         <v>10212868.56118992</v>
       </c>
     </row>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>122911.6626100196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>3154426.617530323</v>
+        <v>3277338.280140342</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7541536.325806242</v>
+        <v>8004286.202438804</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7625011.844510582</v>
+        <v>8087761.721143144</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7541536.325806242</v>
+        <v>8004286.202438804</v>
       </c>
     </row>
     <row r="15">
@@ -580,13 +580,13 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>10212868.56118992</v>
+        <v>10675618.43782248</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7541536.325806242</v>
+        <v>-8004286.202438804</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-4567580.328760721</v>
+        <v>-5030330.205393283</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:08:48+00:00</t>
+          <t>2026-06-09T16:58:46+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2456919.680106931</v>
+        <v>2604153.331510427</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2456919.680106931</v>
+        <v>2604153.331510427</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-2456919.680106931</v>
+        <v>-2604153.331510427</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1350343.627003441</v>
+        <v>1431264.474543929</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1350343.627003441</v>
+        <v>1431264.474543929</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1309475.372996559</v>
+        <v>1228554.525456071</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>851129.1854138965</v>
+        <v>902134.0508961567</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>851129.1854138965</v>
+        <v>902134.0508961567</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-275898.4883518965</v>
+        <v>-326903.3538341567</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>593441.7798956764</v>
+        <v>629004.4402695099</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>593441.7798956764</v>
+        <v>629004.4402695099</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>11104.93997500272</v>
+        <v>-24457.72039883088</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1124,13 +1124,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>435089.9540613988</v>
+        <v>461163.2047028896</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>435089.9540613988</v>
+        <v>461163.2047028896</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>135239.6207917743</v>
+        <v>109166.3701502835</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1193,13 +1193,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>386133.589675829</v>
+        <v>409273.0755930233</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>347668.4253677963</v>
+        <v>370807.9112849906</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-386133.589675829</v>
+        <v>-409273.0755930233</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>279514.4132798024</v>
+        <v>296264.6261664118</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>279514.4132798024</v>
+        <v>296264.6261664118</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>135580.5924213182</v>
+        <v>118830.3795347088</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>255395.1074493354</v>
+        <v>270699.9440399713</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>255395.1074493354</v>
+        <v>270699.9440399713</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-246012.3890019546</v>
+        <v>-261317.2255925906</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1388,13 +1388,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>255388.6036264916</v>
+        <v>270693.0504682916</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>255388.6036264916</v>
+        <v>270693.0504682916</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-183929.1569784916</v>
+        <v>-199233.6038202916</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>258999.392417649</v>
+        <v>274520.2198039467</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>233198.8548539802</v>
+        <v>248719.6822402779</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-258999.392417649</v>
+        <v>-274520.2198039467</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1518,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>192326.0089886613</v>
+        <v>203851.3595292333</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>173167.2211125075</v>
+        <v>184692.5716530795</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-192326.0089886613</v>
+        <v>-203851.3595292333</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>138751.5392449181</v>
+        <v>147066.3799482152</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>138751.5392449181</v>
+        <v>147066.3799482152</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>33651.53434260924</v>
+        <v>25336.69363931211</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>118534.319606518</v>
+        <v>125637.6208798983</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>118534.319606518</v>
+        <v>125637.6208798983</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-118534.319606518</v>
+        <v>-125637.6208798983</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1843,13 +1843,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>40831.02986553439</v>
+        <v>43277.87485861377</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>40831.02986553439</v>
+        <v>43277.87485861377</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-40831.02986553439</v>
+        <v>-43277.87485861377</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>25828.970066658</v>
+        <v>27376.79989833576</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>25828.970066658</v>
+        <v>27376.79989833576</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>17711.94226062157</v>
+        <v>16164.11242894382</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>25538.20551451926</v>
+        <v>27068.61095619489</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>25538.20551451926</v>
+        <v>27068.61095619489</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-6227.79437251926</v>
+        <v>-7758.199814194886</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12767.75723669806</v>
+        <v>13532.87932571591</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12767.75723669806</v>
+        <v>13532.87932571591</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12767.75723669803</v>
+        <v>-13532.87932571588</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12747.78292322775</v>
+        <v>13511.70802923865</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12747.78292322775</v>
+        <v>13511.70802923865</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12747.78292322453</v>
+        <v>-13511.70802923543</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12727.09768159573</v>
+        <v>13489.78320143688</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12727.09768159573</v>
+        <v>13489.78320143688</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12727.0976815944</v>
+        <v>-13489.78320143556</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>12707.72157374711</v>
+        <v>13469.24595872022</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>12707.72157374711</v>
+        <v>13469.24595872022</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-12707.72157376374</v>
+        <v>-13469.24595873685</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4387.273439291298</v>
+        <v>4650.185692142935</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4387.273439291298</v>
+        <v>4650.185692142935</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>462.2239171220098</v>
+        <v>199.3116642703733</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2493.538287706028</v>
+        <v>2642.966350001253</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2245.141456895463</v>
+        <v>2394.569519190688</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2493.538287706028</v>
+        <v>-2642.966350001253</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>6.590658318147608</v>
+        <v>6.985610866735386</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.590658318147608</v>
+        <v>6.985610866735386</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-3.110658318142479</v>
+        <v>-3.505610866730257</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.169865422005418</v>
+        <v>1.239970911870294</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.169865422005418</v>
+        <v>1.239970911870294</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1246793796039116</v>
+        <v>0.05457388973903583</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8821698270891616</v>
+        <v>0.9350348376354874</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8821698270891616</v>
+        <v>0.9350348376354874</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.07126668266949587</v>
+        <v>0.01840167212316994</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7250574374868018</v>
+        <v>0.7685073128990084</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7250574374868018</v>
+        <v>0.7685073128990084</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7250574374868018</v>
+        <v>-0.7685073128990084</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.5637707403518795</v>
+        <v>0.5975553305965419</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5637707403518795</v>
+        <v>0.5975553305965419</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.5637707423556795</v>
+        <v>-0.5975553326003419</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2525372615423412</v>
+        <v>0.267670838530377</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2525372615423412</v>
+        <v>0.267670838530377</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.03606051573508011</v>
+        <v>0.02092693874704422</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1256459615331607</v>
+        <v>0.1331754358787874</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1256459615331607</v>
+        <v>0.1331754358787874</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.125646017363568</v>
+        <v>-0.1331754917091947</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05594819789455457</v>
+        <v>0.05930095603807768</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05594819789455457</v>
+        <v>0.05930095603807768</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05594214568810445</v>
+        <v>-0.05929490383162756</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.003091788268534479</v>
+        <v>0.003277067128005788</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.003091788268534479</v>
+        <v>0.003277067128005788</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>133499.9977132117</v>
+        <v>133499.9975279329</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001467572359311187</v>
+        <v>0.000155551826935039</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001467572359311187</v>
+        <v>0.000155551826935039</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-4.975723593111874e-05</v>
+        <v>-5.8551826935039e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.613836684211996e-05</v>
+        <v>1.71054764701201e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.613836684211996e-05</v>
+        <v>1.71054764701201e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-8.13836684211996e-06</v>
+        <v>-9.105476470120103e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.466141220037101e-05</v>
+        <v>1.554001367459521e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.466141220037101e-05</v>
+        <v>1.554001367459521e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.418112848132801e-05</v>
+        <v>-1.505972995555221e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>4.321271830490105e-06</v>
+        <v>4.580228863339644e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>4.321271830490105e-06</v>
+        <v>4.580228863339644e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-3.21271830490105e-07</v>
+        <v>-5.802288633396445e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.167259001422607e-06</v>
+        <v>3.357060528715411e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.167259001422607e-06</v>
+        <v>3.357060528715411e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.167259001422607e-06</v>
+        <v>-3.357060528715411e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.326123057409306e-06</v>
+        <v>1.405592460309869e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.326123057409306e-06</v>
+        <v>1.405592460309869e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.133417643343059e-07</v>
+        <v>-4.928111672348692e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.912808317055503e-07</v>
+        <v>2.027435488320134e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.912808317055503e-07</v>
+        <v>2.027435488320134e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.912808317055503e-07</v>
+        <v>-2.027435488320134e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7541536.325806242</v>
+        <v>8004286.202438804</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7625011.844510582</v>
+        <v>8087761.721143144</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10212868.56118992</v>
+        <v>10675618.43782248</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7541536.325806242</v>
+        <v>8004286.202438804</v>
       </c>
     </row>
     <row r="12">
@@ -4563,7 +4563,7 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3131305694.853109</v>
+        <v>3273186628.237342</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
@@ -4988,7 +4988,7 @@
         <v>159029980.3263338</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2416566757.341383</v>
+        <v>2558447690.725616</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.04</v>
@@ -5006,10 +5006,10 @@
         <v>0.04312</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>279518.4082718074</v>
+        <v>295929.4312833587</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>362190.5254546798</v>
+        <v>378601.548466231</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3169303197.190613</v>
+        <v>3312905815.272311</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
@@ -5037,7 +5037,7 @@
         <v>168986345.7344508</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2442518245.417933</v>
+        <v>2586120863.499631</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.04</v>
@@ -5055,10 +5055,10 @@
         <v>0.04312</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>282520.1538753192</v>
+        <v>299130.3199747737</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>366585.6042744216</v>
+        <v>383195.7703738762</v>
       </c>
     </row>
     <row r="8">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3146326464.579185</v>
+        <v>3288887996.102523</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
@@ -5086,7 +5086,7 @@
         <v>168969242.5220673</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2430500362.055247</v>
+        <v>2573061893.578585</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.04</v>
@@ -5104,10 +5104,10 @@
         <v>0.04312</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>281130.0744917768</v>
+        <v>297619.8206372689</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>363927.9414114685</v>
+        <v>380417.6875569607</v>
       </c>
     </row>
     <row r="9">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2881318553.009124</v>
+        <v>3011872451.451613</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
@@ -5135,7 +5135,7 @@
         <v>115233339.1487748</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2215606385.526245</v>
+        <v>2346160283.968735</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.04</v>
@@ -5153,10 +5153,10 @@
         <v>0.04312</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>256273.8100893528</v>
+        <v>271374.6624765102</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>333275.1198428256</v>
+        <v>348375.9722299831</v>
       </c>
     </row>
     <row r="10">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2807089586.432195</v>
+        <v>2934280135.496375</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
@@ -5184,7 +5184,7 @@
         <v>106666507.8312684</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2151891202.723649</v>
+        <v>2279081751.787829</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.04</v>
@@ -5202,10 +5202,10 @@
         <v>0.04312</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>248904.0296247227</v>
+        <v>263615.8515570702</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>324689.2355413834</v>
+        <v>339401.0574737309</v>
       </c>
     </row>
     <row r="11">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2780827269.760019</v>
+        <v>2906827860.907153</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
@@ -5233,7 +5233,7 @@
         <v>106913226.5360041</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2116229657.690788</v>
+        <v>2242230248.837922</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.04</v>
@@ -5251,10 +5251,10 @@
         <v>0.04312</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>244779.1453136163</v>
+        <v>259353.3277034713</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>321651.5371490523</v>
+        <v>336225.7195389073</v>
       </c>
     </row>
     <row r="12">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2788088641.022816</v>
+        <v>2914418248.316189</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
@@ -5282,7 +5282,7 @@
         <v>106954288.9193721</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2118041428.077036</v>
+        <v>2244371035.370409</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.04</v>
@@ -5300,10 +5300,10 @@
         <v>0.04312</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>244988.7083943712</v>
+        <v>259600.9472828571</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>322491.4423290278</v>
+        <v>337103.6812175137</v>
       </c>
     </row>
     <row r="13">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>2779945566.177685</v>
+        <v>2905906206.920924</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
@@ -5331,7 +5331,7 @@
         <v>106935113.0757522</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2111247213.57366</v>
+        <v>2237207854.316899</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.04</v>
@@ -5349,10 +5349,10 @@
         <v>0.04312</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>244202.8381022836</v>
+        <v>258772.3995259382</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>321549.5526368708</v>
+        <v>336119.1140605254</v>
       </c>
     </row>
     <row r="14">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>2792788068.209374</v>
+        <v>2919330608.758256</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
@@ -5380,7 +5380,7 @@
         <v>107322066.296092</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2136295233.72203</v>
+        <v>2262837774.270913</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.0375</v>
@@ -5398,10 +5398,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>233012.1776308807</v>
+        <v>246814.5549759193</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>304617.8351955642</v>
+        <v>318420.2125406028</v>
       </c>
     </row>
     <row r="15">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2792926035.615368</v>
+        <v>2919474827.532289</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
@@ -5429,7 +5429,7 @@
         <v>107333348.9757696</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2138806862.418313</v>
+        <v>2265355654.335234</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.0375</v>
@@ -5447,10 +5447,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>233286.128563637</v>
+        <v>247089.187764281</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>304632.8837175125</v>
+        <v>318435.9429181565</v>
       </c>
     </row>
     <row r="16">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>2790054498.466092</v>
+        <v>2916473179.684572</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
@@ -5478,7 +5478,7 @@
         <v>107387902.5867912</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2148537624.727249</v>
+        <v>2274956305.945729</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.0375</v>
@@ -5496,10 +5496,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>234347.4922177903</v>
+        <v>248136.3598513241</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>304319.676482043</v>
+        <v>318108.5441155768</v>
       </c>
     </row>
     <row r="17">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>2787622121.342249</v>
+        <v>2913930590.409536</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
@@ -5527,7 +5527,7 @@
         <v>106417723.4543805</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2131037426.217979</v>
+        <v>2257345895.285266</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.0375</v>
@@ -5545,10 +5545,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>232438.6926758314</v>
+        <v>246215.5391369423</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>304054.3697578133</v>
+        <v>317831.2162189242</v>
       </c>
     </row>
     <row r="18">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2791260263.036477</v>
+        <v>2917733578.014596</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
@@ -5576,7 +5576,7 @@
         <v>106551417.0948813</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2144480845.701279</v>
+        <v>2270954160.679399</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.0375</v>
@@ -5594,10 +5594,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>233905.0070686935</v>
+        <v>247699.8337715098</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>304451.1928678967</v>
+        <v>318246.0195707129</v>
       </c>
     </row>
     <row r="19">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>2802908640.567328</v>
+        <v>2929909749.008476</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
@@ -5625,7 +5625,7 @@
         <v>106911070.5772904</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2153231755.900424</v>
+        <v>2280232864.341573</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.0375</v>
@@ -5643,10 +5643,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>234859.4952918416</v>
+        <v>248711.8900228117</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>305721.7166098803</v>
+        <v>319574.1113408503</v>
       </c>
     </row>
     <row r="20">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>2809376592.82677</v>
+        <v>2936670767.226046</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
@@ -5674,7 +5674,7 @@
         <v>106936208.3821319</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2160064410.605867</v>
+        <v>2287358585.005143</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.0375</v>
@@ -5692,10 +5692,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>235604.7535907805</v>
+        <v>249489.1139115319</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>306427.1957107999</v>
+        <v>320311.5560315513</v>
       </c>
     </row>
     <row r="21">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>2819847342.704478</v>
+        <v>2947615951.704095</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
@@ -5723,7 +5723,7 @@
         <v>107032449.9192543</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2170069215.963748</v>
+        <v>2297837824.963365</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.0375</v>
@@ -5741,10 +5741,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>236696.0079485179</v>
+        <v>250632.1162850041</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>307569.2720455311</v>
+        <v>321505.3803820173</v>
       </c>
     </row>
     <row r="22">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2820880505.400382</v>
+        <v>2948695927.487547</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
@@ -5772,7 +5772,7 @@
         <v>107504855.7115974</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2171137032.244217</v>
+        <v>2298952454.331382</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.0375</v>
@@ -5790,10 +5790,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>236812.4778974718</v>
+        <v>250753.6922788992</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>307681.9622232834</v>
+        <v>321623.1766047109</v>
       </c>
     </row>
     <row r="23">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>2907124641.609815</v>
+        <v>3038847826.060911</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
@@ -5821,7 +5821,7 @@
         <v>107436888.0729907</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2258977438.239259</v>
+        <v>2390700622.690355</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.0375</v>
@@ -5839,10 +5839,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>246393.4964579188</v>
+        <v>260760.9422907441</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>317088.8708138351</v>
+        <v>331456.3166466604</v>
       </c>
     </row>
     <row r="24">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>2905429817.13824</v>
+        <v>3037076208.295617</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
@@ -5870,7 +5870,7 @@
         <v>107184053.179774</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2247502744.749332</v>
+        <v>2379149135.906709</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.0375</v>
@@ -5888,10 +5888,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>245141.9169592012</v>
+        <v>259500.9867153894</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>316904.0111864812</v>
+        <v>331263.0809426694</v>
       </c>
     </row>
     <row r="25">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2914194882.912043</v>
+        <v>3046238423.320994</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
@@ -5919,7 +5919,7 @@
         <v>107194547.5382319</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2223183703.758221</v>
+        <v>2355227244.167172</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.0375</v>
@@ -5937,10 +5937,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>242489.3656592759</v>
+        <v>256891.7536846309</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>317860.0434009393</v>
+        <v>332262.4314262943</v>
       </c>
     </row>
     <row r="26">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3077529531.212519</v>
+        <v>3216973841.336464</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
@@ -5968,7 +5968,7 @@
         <v>107211163.3616333</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2377929163.170564</v>
+        <v>2517373473.29451</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.0375</v>
@@ -5986,10 +5986,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>259367.9206019552</v>
+        <v>274577.5329473452</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>335675.447134607</v>
+        <v>350885.059479997</v>
       </c>
     </row>
     <row r="27">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3137611584.903619</v>
+        <v>3279778241.131091</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
@@ -6017,7 +6017,7 @@
         <v>107220548.4053871</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2450348486.567435</v>
+        <v>2592515142.794907</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.0375</v>
@@ -6035,10 +6035,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>267266.9150765436</v>
+        <v>282773.4619391457</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>342228.7783156662</v>
+        <v>357735.3251782683</v>
       </c>
     </row>
     <row r="28">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3132475429.811056</v>
+        <v>3274409364.436247</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
@@ -6066,7 +6066,7 @@
         <v>107244908.9822976</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2448501830.507803</v>
+        <v>2590435765.132995</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.0375</v>
@@ -6084,10 +6084,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>267065.4947190023</v>
+        <v>282546.657933093</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>341668.562356806</v>
+        <v>357149.7255708967</v>
       </c>
     </row>
     <row r="29">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3117051456.181883</v>
+        <v>3258286523.309532</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
@@ -6115,7 +6115,7 @@
         <v>108592021.8578287</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2427132708.02054</v>
+        <v>2568367775.148189</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.0375</v>
@@ -6133,10 +6133,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>264734.6999457804</v>
+        <v>280139.6355697388</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>339986.2229374585</v>
+        <v>355391.1585614169</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3099592040.943802</v>
+        <v>3240036013.757538</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
@@ -6164,7 +6164,7 @@
         <v>107978396.0840361</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2413428427.101261</v>
+        <v>2553872399.914997</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.0375</v>
@@ -6182,10 +6182,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>263239.932607699</v>
+        <v>278558.581183928</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>338081.8717501467</v>
+        <v>353400.5203263757</v>
       </c>
     </row>
     <row r="31">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3117529667.747241</v>
+        <v>3258786402.865773</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
@@ -6213,7 +6213,7 @@
         <v>112655549.2029514</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2425473003.61229</v>
+        <v>2566729738.730822</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.0375</v>
@@ -6231,10 +6231,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>264553.6709698761</v>
+        <v>279960.9699870869</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>340038.3829181828</v>
+        <v>355445.6819353936</v>
       </c>
     </row>
     <row r="32">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3113281481.525022</v>
+        <v>3254345729.328314</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
@@ -6262,7 +6262,7 @@
         <v>112685017.5580367</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2420059839.073637</v>
+        <v>2561124086.876928</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.0375</v>
@@ -6280,10 +6280,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>263963.2407535299</v>
+        <v>279349.5445975163</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>339575.0204077042</v>
+        <v>354961.3242516907</v>
       </c>
     </row>
     <row r="33">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3098756108.186975</v>
+        <v>3239162204.494441</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
@@ -6311,7 +6311,7 @@
         <v>112893900.0040528</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2404543758.234733</v>
+        <v>2544949854.542199</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.0375</v>
@@ -6329,10 +6329,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>262270.854922443</v>
+        <v>277585.3721936596</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>337990.6940379342</v>
+        <v>353305.2113091508</v>
       </c>
     </row>
     <row r="34">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3242110616.116458</v>
+        <v>3389012172.583979</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>334970000</v>
@@ -6360,7 +6360,7 @@
         <v>112902235.561008</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2546481619.551023</v>
+        <v>2693383176.018544</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.0375</v>
@@ -6378,10 +6378,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>277752.4464325994</v>
+        <v>293775.4431745922</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>353626.8034756986</v>
+        <v>369649.8002176914</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3277107093.689361</v>
+        <v>3425594357.011171</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>334970000</v>
@@ -6409,7 +6409,7 @@
         <v>123415130.4064669</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>2558092448.321908</v>
+        <v>2706579711.643719</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.0375</v>
@@ -6427,10 +6427,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>279018.8746178506</v>
+        <v>295214.8291988956</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>357443.9750538352</v>
+        <v>373639.9296348803</v>
       </c>
     </row>
     <row r="36">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3381796950.610221</v>
+        <v>3535027760.574637</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>334970000</v>
@@ -6458,7 +6458,7 @@
         <v>125802289.7933941</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2646996811.112102</v>
+        <v>2800227621.076518</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.0375</v>
@@ -6476,10 +6476,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>288715.9421615233</v>
+        <v>305429.2897112179</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>368862.8141505707</v>
+        <v>385576.1617002653</v>
       </c>
     </row>
     <row r="38">
@@ -6501,10 +6501,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="11" t="n">
-        <v>7885254.172933893</v>
+        <v>8348004.049566455</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>10212868.56118992</v>
+        <v>10675618.43782248</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3154426.617530323</v>
+        <v>6084952.074495915</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>3277338.280140342</v>
+        <v>6207863.737105935</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3154426.617530323</v>
+        <v>6084952.074495915</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-5030330.205393283</v>
+        <v>-2099804.74842769</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:58:46+00:00</t>
+          <t>2026-06-09T22:29:29+00:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="9" t="n">
-        <v>-2930525.456965593</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:29:29+00:00</t>
+          <t>2026-06-09T23:17:00+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6084952.074495915</v>
+        <v>10152205.00143894</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>6207863.737105935</v>
+        <v>10275116.66404896</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>83475.51870433975</v>
+        <v>5964.770934815006</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>8087761.721143144</v>
+        <v>8010250.973373619</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6084952.074495915</v>
+        <v>10152205.00143894</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2099804.74842769</v>
+        <v>836069.708816571</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:17:00+00:00</t>
+          <t>2026-06-10T10:58:28+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>572733555.2197744</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>1802372.802499282</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>1802372.802499282</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>2604153.331510427</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-2604153.331510427</v>
+        <v>-801780.5290111455</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>-53957591.71043837</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>489338.0926723001</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>489338.0926723001</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>370807.9112849906</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-409273.0755930233</v>
+        <v>80065.01707927676</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1435,13 +1435,13 @@
         <v>323394.9088048668</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>248719.6822402779</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-274520.2198039467</v>
+        <v>48874.68900092009</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>240144.3939968634</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>184692.5716530795</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-203851.3595292333</v>
+        <v>36293.03446763009</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1728,12 +1728,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50000340.64647674</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>495610843.871423</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>539.2093880709065</v>
+        <v>495610843.871423</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
@@ -1765,44 +1765,40 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49997665.28166009</v>
+        <v>15987446.57649752</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>43277.87485861377</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>43277.87485861377</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>-43277.87485861377</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49997665.28166009</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1812,44 +1808,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>10113369.18090356</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>43540.91232727958</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>15987446.57649752</v>
+        <v>10113369.18090356</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>43277.87485861377</v>
+        <v>27376.79989833576</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>43277.87485861377</v>
+        <v>27376.79989833576</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-43277.87485861377</v>
+        <v>16164.11242894382</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1862,59 +1858,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10113369.18090356</v>
+        <v>10000143.505486</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>10000122.636328</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>-20.869158</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>19310.411142</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>43540.91232727958</v>
+        <v>19310.411142</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>10113369.18090356</v>
+        <v>9999519.915798903</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>27376.79989833576</v>
+        <v>27068.61095619489</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>27376.79989833576</v>
+        <v>27068.61095619489</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>16164.11242894382</v>
+        <v>-7758.199814194886</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1927,59 +1923,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>10000143.505486</v>
+        <v>4997665.827264</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>4987120.646667</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-20.869158</v>
+        <v>-10545.180597</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>19310.411142</v>
+        <v>3.225e-11</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>19310.411142</v>
+        <v>3.225e-11</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9999519.915798903</v>
+        <v>4999233.117450742</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>27068.61095619489</v>
+        <v>13532.87932571591</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>27068.61095619489</v>
+        <v>13532.87932571591</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-7758.199814194886</v>
+        <v>-13532.87932571588</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1992,17 +1988,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2011,40 +2007,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>5000000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>5000000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-10545.180597</v>
+        <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>3.218e-09</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>3.218e-09</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4999233.117450742</v>
+        <v>4991412.147209223</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13532.87932571591</v>
+        <v>13511.70802923865</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13532.87932571591</v>
+        <v>13511.70802923865</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13532.87932571588</v>
+        <v>-13511.70802923543</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2057,17 +2053,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2079,37 +2075,37 @@
         <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5000000</v>
+        <v>4997775.722557</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>-2224.277443</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>1.3225e-09</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>1.3225e-09</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4991412.147209223</v>
+        <v>4983312.81205645</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13511.70802923865</v>
+        <v>13489.78320143688</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13511.70802923865</v>
+        <v>13489.78320143688</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13511.70802923543</v>
+        <v>-13489.78320143556</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2122,17 +2118,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2141,40 +2137,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>4983790.597531</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>4442753.639281</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-2224.277443</v>
+        <v>-541036.95825</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>-1.663e-08</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>-1.663e-08</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4983312.81205645</v>
+        <v>4975726.070058748</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13489.78320143688</v>
+        <v>13469.24595872022</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13489.78320143688</v>
+        <v>13469.24595872022</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13489.78320143556</v>
+        <v>-13469.24595873685</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2187,67 +2183,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4983790.597531</v>
+        <v>50000340.64647674</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-541036.95825</v>
+        <v>539.2093880709065</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>5964.770934815006</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>77510.74776952475</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>77510.74776952475</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>5964.770934815006</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4975726.070058748</v>
+        <v>49997665.28166009</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>13469.24595872022</v>
+        <v>0</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>13469.24595872022</v>
+        <v>5964.770934815006</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-13469.24595873685</v>
+        <v>77510.74776952475</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0</v>
+        <v>49997665.28166009</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2345,13 +2345,13 @@
         <v>3113.511501423833</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>3113.511501423833</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>3113.511501423833</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>2394.569519190688</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2642.966350001253</v>
+        <v>470.5451514225803</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>83475.51870433975</v>
+        <v>5964.770934815006</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8087761.721143144</v>
+        <v>8010250.973373619</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>5964.770934815006</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>83475.51870433975</v>
+        <v>5964.770934815006</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10152205.00143894</v>
+        <v>10152205.00022014</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>122911.6626100196</v>
+        <v>122911.67199757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>10275116.66404896</v>
+        <v>10275116.67221771</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8004286.202438804</v>
+        <v>7640168.688929425</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>8010250.973373619</v>
+        <v>7646133.453841745</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>8004286.202438804</v>
+        <v>7640168.688929425</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2671332.235383678</v>
+        <v>-2671332.408489357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>10675618.43782248</v>
+        <v>10311501.09741878</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10152205.00143894</v>
+        <v>10152205.00022014</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-8004286.202438804</v>
+        <v>-7640168.688929425</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>836069.708816571</v>
+        <v>1200187.129225802</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T10:58:28+00:00</t>
+          <t>2026-06-23T21:44:29+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>572733555.2197744</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1802372.802499282</v>
+        <v>1802372.703376638</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1802372.802499282</v>
+        <v>1802372.703376638</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2604153.331510427</v>
+        <v>2488301.650589254</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2604153.331510427</v>
+        <v>2488301.650589254</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-801780.5290111455</v>
+        <v>-685928.9472126159</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1431264.474543929</v>
+        <v>1367591.420729352</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1431264.474543929</v>
+        <v>1367591.420729352</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1228554.525456071</v>
+        <v>1292227.579270648</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>902134.0508961567</v>
+        <v>862000.5668390068</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>902134.0508961567</v>
+        <v>862000.5668390068</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-326903.3538341567</v>
+        <v>-286769.8697770069</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>629004.4402695099</v>
+        <v>601021.7478410888</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>629004.4402695099</v>
+        <v>601021.7478410888</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-24457.72039883088</v>
+        <v>3524.972029590343</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1124,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>461163.2047028896</v>
+        <v>440647.3111887249</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>461163.2047028896</v>
+        <v>440647.3111887249</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>109166.3701502835</v>
+        <v>129682.2636644482</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1193,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>409273.0755930233</v>
+        <v>391065.6324330887</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>370807.9112849906</v>
+        <v>352600.468125056</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>80065.01707927676</v>
+        <v>98272.46023921133</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1258,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>296264.6261664118</v>
+        <v>283084.6207790353</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>296264.6261664118</v>
+        <v>283084.6207790353</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>118830.3795347088</v>
+        <v>132010.3849220854</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1323,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>270699.9440399713</v>
+        <v>258657.2416526627</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>270699.9440399713</v>
+        <v>258657.2416526627</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-261317.2255925906</v>
+        <v>-249274.5232052819</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1388,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>270693.0504682916</v>
+        <v>258650.6547571901</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>270693.0504682916</v>
+        <v>258650.6547571901</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-199233.6038202916</v>
+        <v>-187191.2081091901</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>274520.2198039467</v>
+        <v>262307.5637647223</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>248719.6822402779</v>
+        <v>236507.0262010535</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>48874.68900092009</v>
+        <v>61087.34504014455</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>203851.3595292333</v>
+        <v>194782.5683894157</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>184692.5716530795</v>
+        <v>175623.7805132619</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>36293.03446763009</v>
+        <v>45361.82560744767</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>147066.3799482152</v>
+        <v>140523.7977132012</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>147066.3799482152</v>
+        <v>140523.7977132012</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>25336.69363931211</v>
+        <v>31879.27587432615</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>125637.6208798983</v>
+        <v>120048.3457056015</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>125637.6208798983</v>
+        <v>120048.3457056015</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-125637.6208798983</v>
+        <v>-120048.3457056015</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1774,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>43277.87485861377</v>
+        <v>41352.5602128135</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>43277.87485861377</v>
+        <v>41352.5602128135</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-43277.87485861377</v>
+        <v>-41352.5602128135</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1839,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>27376.79989833576</v>
+        <v>26158.88071973453</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>27376.79989833576</v>
+        <v>26158.88071973453</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>16164.11242894382</v>
+        <v>17382.03160754504</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1904,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>27068.61095619489</v>
+        <v>25864.40226328447</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>27068.61095619489</v>
+        <v>25864.40226328447</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-7758.199814194886</v>
+        <v>-6553.99112128447</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1969,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13532.87932571591</v>
+        <v>12930.83842489144</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13532.87932571591</v>
+        <v>12930.83842489144</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13532.87932571588</v>
+        <v>-12930.8384248914</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2034,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13511.70802923865</v>
+        <v>12910.60898166625</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13511.70802923865</v>
+        <v>12910.60898166625</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13511.70802923543</v>
+        <v>-12910.60898166303</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2099,13 +2102,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13489.78320143688</v>
+        <v>12889.65952967051</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13489.78320143688</v>
+        <v>12889.65952967051</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13489.78320143556</v>
+        <v>-12889.65952966918</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2164,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13469.24595872022</v>
+        <v>12870.035932883</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13469.24595872022</v>
+        <v>12870.035932883</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13469.24595873685</v>
+        <v>-12870.03593289963</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2211,16 +2214,16 @@
         <v>539.2093880709065</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>77510.74776952475</v>
+        <v>77510.75379201942</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>77510.74776952475</v>
+        <v>77510.75379201942</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>49997665.28166009</v>
@@ -2232,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>77510.74776952475</v>
+        <v>77510.75379201942</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>49997665.28166009</v>
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4650.185692142935</v>
+        <v>4443.311610455171</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4650.185692142935</v>
+        <v>4443.311610455171</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>199.3116642703733</v>
+        <v>406.1857459581371</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2642.966350001253</v>
+        <v>2525.387983719667</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2394.569519190688</v>
+        <v>2276.991152909102</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>470.5451514225803</v>
+        <v>588.1235177041658</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>6.985610866735386</v>
+        <v>6.674840087081211</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.985610866735386</v>
+        <v>6.674840087081211</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-3.505610866730257</v>
+        <v>-3.194840087076083</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.239970911870294</v>
+        <v>1.184807987055028</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.239970911870294</v>
+        <v>1.184807987055028</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.05457388973903583</v>
+        <v>0.1097368145543018</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.9350348376354874</v>
+        <v>0.8934376872875476</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9350348376354874</v>
+        <v>0.8934376872875476</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.01840167212316994</v>
+        <v>0.0599988224711099</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7685073128990084</v>
+        <v>0.7343185180526139</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7685073128990084</v>
+        <v>0.7343185180526139</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7685073128990084</v>
+        <v>-0.7343185180526139</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.5975553305965419</v>
+        <v>0.5709717233045456</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5975553305965419</v>
+        <v>0.5709717233045456</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.5975553326003419</v>
+        <v>-0.5709717253083456</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.267670838530377</v>
+        <v>0.2557628927876668</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.267670838530377</v>
+        <v>0.2557628927876668</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.02092693874704422</v>
+        <v>0.03283488448975445</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1331754358787874</v>
+        <v>0.1272508238687032</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1331754358787874</v>
+        <v>0.1272508238687032</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.1331754917091947</v>
+        <v>-0.1272508796991105</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05930095603807768</v>
+        <v>0.0566628182010636</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05930095603807768</v>
+        <v>0.0566628182010636</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05929490383162756</v>
+        <v>-0.05665676599461348</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.003277067128005788</v>
+        <v>0.003131279347126238</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.003277067128005788</v>
+        <v>0.003131279347126238</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>133499.9975279329</v>
+        <v>133499.9976737206</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.000155551826935039</v>
+        <v>0.0001486317503010217</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.000155551826935039</v>
+        <v>0.0001486317503010217</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-5.8551826935039e-05</v>
+        <v>-5.163175030102164e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.71054764701201e-05</v>
+        <v>1.634450046381421e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.71054764701201e-05</v>
+        <v>1.634450046381421e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-9.105476470120103e-06</v>
+        <v>-8.344500463814206e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.554001367459521e-05</v>
+        <v>1.484868083948305e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.554001367459521e-05</v>
+        <v>1.484868083948305e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.505972995555221e-05</v>
+        <v>-1.436839712044005e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>4.580228863339644e-06</v>
+        <v>4.376466970212635e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>4.580228863339644e-06</v>
+        <v>4.376466970212635e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-5.802288633396445e-07</v>
+        <v>-3.764669702126345e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.357060528715411e-06</v>
+        <v>3.207714059557918e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.357060528715411e-06</v>
+        <v>3.207714059557918e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.357060528715411e-06</v>
+        <v>-3.207714059557918e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.405592460309869e-06</v>
+        <v>1.343061484408163e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.405592460309869e-06</v>
+        <v>1.343061484408163e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.928111672348692e-07</v>
+        <v>-4.302801913331631e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.027435488320134e-07</v>
+        <v>1.937240411694252e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.027435488320134e-07</v>
+        <v>1.937240411694252e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.027435488320134e-07</v>
+        <v>-1.937240411694252e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,377 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>8004286.202438804</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>5964.770934815006</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2431714480.2962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>8010250.973373619</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1431714480.2962</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.04124672584310142</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.0364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>10675618.43782248</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03680496665912168</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>8004286.202438804</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.03941483592081255</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-2671332.235383678</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-18.31889922288867</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>364118.1373055246</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>180470.6204848008</v>
+        <v>8348004.6733626</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>7983886.536057075</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>364118.1373055246</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3069902.203300723</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1431714480.2962</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>4913984.332756353</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>7640168.688929425</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5964.764912320331</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7646133.453841745</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>10311501.09741878</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>7640168.688929425</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-2671332.408489357</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>180470.6204848008</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2 (SoM) → 2 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5021,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5964.770934815006</v>
+        <v>5964.764912320331</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5066,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5176,25 @@
         <v>2558447690.725616</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>295929.4312833587</v>
+        <v>279700.6628648615</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>378601.548466231</v>
+        <v>362372.7836082564</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5225,25 @@
         <v>2586120863.499631</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>299130.3199747737</v>
+        <v>282901.5516941324</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>383195.7703738762</v>
+        <v>366967.0057137655</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5274,25 @@
         <v>2573061893.578585</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>297619.8206372689</v>
+        <v>281391.0522915734</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>380417.6875569607</v>
+        <v>364188.9227772035</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5323,25 @@
         <v>2346160283.968735</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>271374.6624765102</v>
+        <v>255145.8930004883</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>348375.9722299831</v>
+        <v>332147.2060702533</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5372,25 @@
         <v>2279081751.787829</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>263615.8515570702</v>
+        <v>247387.0817468918</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>339401.0574737309</v>
+        <v>323172.2909274696</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5421,25 @@
         <v>2242230248.837922</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>259353.3277034713</v>
+        <v>243124.5577097146</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>336225.7195389073</v>
+        <v>319996.9528558906</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5470,25 @@
         <v>2244371035.370409</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>259600.9472828571</v>
+        <v>243372.1772997648</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>337103.6812175137</v>
+        <v>320874.9145723091</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5519,25 @@
         <v>2237207854.316899</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03696000015803837</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>258772.3995259382</v>
+        <v>242543.6295071621</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>336119.1140605254</v>
+        <v>319890.3473729173</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5568,25 @@
         <v>2262837774.270913</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>246814.5549759193</v>
+        <v>236628.1463111601</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>318420.2125406028</v>
+        <v>308233.8100403404</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5617,25 @@
         <v>2265355654.335234</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>247089.187764281</v>
+        <v>236902.7791231647</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>318435.9429181565</v>
+        <v>308249.5404192483</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5666,25 @@
         <v>2274956305.945729</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>248136.3598513241</v>
+        <v>237949.9513003584</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>318108.5441155768</v>
+        <v>307922.1415884829</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5715,25 @@
         <v>2257345895.285266</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>246215.5391369423</v>
+        <v>236029.130420614</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>317831.2162189242</v>
+        <v>307644.8136679553</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5764,25 @@
         <v>2270954160.679399</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>247699.8337715098</v>
+        <v>237513.4251829637</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>318246.0195707129</v>
+        <v>308059.6170554543</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5813,25 @@
         <v>2280232864.341573</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>248711.8900228117</v>
+        <v>238525.4815213931</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>319574.1113408503</v>
+        <v>309387.7089399265</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5862,25 @@
         <v>2287358585.005143</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>249489.1139115319</v>
+        <v>239302.7054770241</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>320311.5560315513</v>
+        <v>310125.1536941137</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5911,25 @@
         <v>2297837824.963365</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>250632.1162850041</v>
+        <v>240445.7079488969</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>321505.3803820173</v>
+        <v>311318.9781473554</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5960,25 @@
         <v>2298952454.331382</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>250753.6922788992</v>
+        <v>240567.2839532584</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>321623.1766047109</v>
+        <v>311436.7743801901</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6009,25 @@
         <v>2390700622.690355</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>260760.9422907441</v>
+        <v>250574.5348266227</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>331456.3166466604</v>
+        <v>321269.9152686698</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6058,25 @@
         <v>2379149135.906709</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>259500.9867153894</v>
+        <v>249314.579142799</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>331263.0809426694</v>
+        <v>321076.6795480434</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6107,25 @@
         <v>2355227244.167172</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>256891.7536846309</v>
+        <v>246705.3458874128</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>332262.4314262943</v>
+        <v>322076.0301177018</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6156,25 @@
         <v>2517373473.29451</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>274577.5329473452</v>
+        <v>264391.1266726874</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>350885.059479997</v>
+        <v>340698.6597746177</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6205,25 @@
         <v>2592515142.794907</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>282773.4619391457</v>
+        <v>272587.0563700715</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>357735.3251782683</v>
+        <v>347548.926062625</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6254,25 @@
         <v>2590435765.132995</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>282546.657933093</v>
+        <v>272360.2523444934</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>357149.7255708967</v>
+        <v>346963.3264048395</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6303,25 @@
         <v>2568367775.148189</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>280139.6355697388</v>
+        <v>269953.2297739198</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>355391.1585614169</v>
+        <v>345204.7592439654</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6352,25 @@
         <v>2553872399.914997</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>278558.581183928</v>
+        <v>268372.1752519968</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>353400.5203263757</v>
+        <v>343214.1208375512</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6401,25 @@
         <v>2566729738.730822</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>279960.9699870869</v>
+        <v>269774.5641758866</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>355445.6819353936</v>
+        <v>345259.2826226361</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6450,25 @@
         <v>2561124086.876928</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>279349.5445975163</v>
+        <v>269163.1387336787</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>354961.3242516907</v>
+        <v>344774.924897235</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6499,25 @@
         <v>2544949854.542199</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>277585.3721936596</v>
+        <v>267398.9661779453</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>353305.2113091508</v>
+        <v>343118.8118121212</v>
       </c>
     </row>
     <row r="34">
@@ -6363,25 +6548,25 @@
         <v>2693383176.018544</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K34" t="n">
         <v>2</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>293775.4431745922</v>
+        <v>283589.0385526734</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>369649.8002176914</v>
+        <v>359463.4021277596</v>
       </c>
     </row>
     <row r="35">
@@ -6412,25 +6597,25 @@
         <v>2706579711.643719</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>295214.8291988956</v>
+        <v>285028.4247008928</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>373639.9296348803</v>
+        <v>363453.5318884568</v>
       </c>
     </row>
     <row r="36">
@@ -6461,25 +6646,25 @@
         <v>2800227621.076518</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>305429.2897112179</v>
+        <v>295242.8860925731</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>385576.1617002653</v>
+        <v>375389.7649814264</v>
       </c>
     </row>
     <row r="38">
@@ -6500,11 +6685,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="11" t="n">
-        <v>8348004.049566455</v>
-      </c>
-      <c r="O38" s="11" t="n">
-        <v>10675618.43782248</v>
+      <c r="N38" s="12" t="n">
+        <v>7983886.536057075</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <v>10311501.09741878</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7640168.688929425</v>
+        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7646133.453841745</v>
+        <v>7809380.680484595</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7640168.688929425</v>
+        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2671332.408489357</v>
+        <v>-2508085.181846506</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7640168.688929425</v>
+        <v>-7803415.915572274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1200187.129225802</v>
+        <v>1036939.902582951</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:44:29+00:00</t>
+          <t>2026-06-25T11:42:52+00:00</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2488301.650589254</v>
+        <v>2540242.205247048</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2488301.650589254</v>
+        <v>2540242.205247048</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-685928.9472126159</v>
+        <v>-737869.5018704099</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1367591.420729352</v>
+        <v>1396138.384446995</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1367591.420729352</v>
+        <v>1396138.384446995</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1292227.579270648</v>
+        <v>1263680.615553005</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>862000.5668390068</v>
+        <v>879993.8786813826</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>862000.5668390068</v>
+        <v>879993.8786813826</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-286769.8697770069</v>
+        <v>-304763.1816193826</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>601021.7478410888</v>
+        <v>613567.4144554521</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>601021.7478410888</v>
+        <v>613567.4144554521</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>3524.972029590343</v>
+        <v>-9020.694584773077</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1127,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>440647.3111887249</v>
+        <v>449845.3381828347</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>440647.3111887249</v>
+        <v>449845.3381828347</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>129682.2636644482</v>
+        <v>120484.2366703383</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>391065.6324330887</v>
+        <v>399228.6965259673</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>352600.468125056</v>
+        <v>360763.5322179346</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>98272.46023921133</v>
+        <v>90109.39614633274</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>283084.6207790353</v>
+        <v>288993.7002569484</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>283084.6207790353</v>
+        <v>288993.7002569484</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>132010.3849220854</v>
+        <v>126101.3054441722</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>258657.2416526627</v>
+        <v>264056.4265121482</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>258657.2416526627</v>
+        <v>264056.4265121482</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-249274.5232052819</v>
+        <v>-254673.7080647675</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>258650.6547571901</v>
+        <v>264049.702122492</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>258650.6547571901</v>
+        <v>264049.702122492</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-187191.2081091901</v>
+        <v>-192590.2554744919</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>262307.5637647223</v>
+        <v>267782.9450753636</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>236507.0262010535</v>
+        <v>241982.4075116948</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>61087.34504014455</v>
+        <v>55611.96372950323</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>194782.5683894157</v>
+        <v>198848.4398392941</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>175623.7805132619</v>
+        <v>179689.6519631402</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>45361.82560744767</v>
+        <v>41295.95415756934</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>140523.7977132012</v>
+        <v>143457.0771225184</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>140523.7977132012</v>
+        <v>143457.0771225184</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>31879.27587432615</v>
+        <v>28945.996465009</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>120048.3457056015</v>
+        <v>122554.2226197703</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>120048.3457056015</v>
+        <v>122554.2226197703</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-120048.3457056015</v>
+        <v>-122554.2226197703</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>41352.5602128135</v>
+        <v>42215.74933357976</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>41352.5602128135</v>
+        <v>42215.74933357976</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-41352.5602128135</v>
+        <v>-42215.74933357976</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26158.88071973453</v>
+        <v>26704.91852567672</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26158.88071973453</v>
+        <v>26704.91852567672</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>17382.03160754504</v>
+        <v>16835.99380160285</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>25864.40226328447</v>
+        <v>26404.29315598599</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>25864.40226328447</v>
+        <v>26404.29315598599</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-6553.99112128447</v>
+        <v>-7093.882013985991</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>12930.83842489144</v>
+        <v>13200.75542624058</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>12930.83842489144</v>
+        <v>13200.75542624058</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-12930.8384248914</v>
+        <v>-13200.75542624055</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12910.60898166625</v>
+        <v>13180.10371568246</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12910.60898166625</v>
+        <v>13180.10371568246</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12910.60898166303</v>
+        <v>-13180.10371567924</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12889.65952967051</v>
+        <v>13158.7169669642</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12889.65952967051</v>
+        <v>13158.7169669642</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12889.65952966918</v>
+        <v>-13158.71696696287</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2167,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12870.035932883</v>
+        <v>13138.68374922045</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12870.035932883</v>
+        <v>13138.68374922045</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12870.03593289963</v>
+        <v>-13138.68374923708</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4443.311610455171</v>
+        <v>4536.060843455039</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4443.311610455171</v>
+        <v>4536.060843455039</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>406.1857459581371</v>
+        <v>313.4365129582695</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2525.387983719667</v>
+        <v>2578.10267470959</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2276.991152909102</v>
+        <v>2329.705843899025</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>588.1235177041658</v>
+        <v>535.4088267142429</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>6.674840087081211</v>
+        <v>6.814170017716019</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.674840087081211</v>
+        <v>6.814170017716019</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-3.194840087076083</v>
+        <v>-3.33417001771089</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2496,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.184807987055028</v>
+        <v>1.209539548036008</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.184807987055028</v>
+        <v>1.209539548036008</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1097368145543018</v>
+        <v>0.08500525357332127</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8934376872875476</v>
+        <v>0.9120872143731815</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8934376872875476</v>
+        <v>0.9120872143731815</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.0599988224711099</v>
+        <v>0.04134929538547594</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2626,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7343185180526139</v>
+        <v>0.7496466078419327</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7343185180526139</v>
+        <v>0.7496466078419327</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7343185180526139</v>
+        <v>-0.7496466078419327</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.5709717233045456</v>
+        <v>0.5828901287741283</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5709717233045456</v>
+        <v>0.5828901287741283</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.5709717253083456</v>
+        <v>-0.5828901307779283</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2756,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2557628927876668</v>
+        <v>0.2611016613043888</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2557628927876668</v>
+        <v>0.2611016613043888</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.03283488448975445</v>
+        <v>0.02749611597303243</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1272508238687032</v>
+        <v>0.1299070445768462</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1272508238687032</v>
+        <v>0.1299070445768462</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.1272508796991105</v>
+        <v>-0.1299071004072535</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0566628182010636</v>
+        <v>0.05784559208426222</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0566628182010636</v>
+        <v>0.05784559208426222</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05665676599461348</v>
+        <v>-0.0578395398778121</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.003131279347126238</v>
+        <v>0.003196641352588766</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.003131279347126238</v>
+        <v>0.003196641352588766</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>133499.9976737206</v>
+        <v>133499.9976083587</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3016,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001486317503010217</v>
+        <v>0.0001517342742850272</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001486317503010217</v>
+        <v>0.0001517342742850272</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-5.163175030102164e-05</v>
+        <v>-5.473427428502721e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.634450046381421e-05</v>
+        <v>1.668567389810986e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.634450046381421e-05</v>
+        <v>1.668567389810986e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-8.344500463814206e-06</v>
+        <v>-8.685673898109861e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.484868083948305e-05</v>
+        <v>1.515863068762813e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.484868083948305e-05</v>
+        <v>1.515863068762813e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.436839712044005e-05</v>
+        <v>-1.467834696858513e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>4.376466970212635e-06</v>
+        <v>4.467820895015332e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>4.376466970212635e-06</v>
+        <v>4.467820895015332e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-3.764669702126345e-07</v>
+        <v>-4.678208950153324e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.207714059557918e-06</v>
+        <v>3.274671555405573e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.207714059557918e-06</v>
+        <v>3.274671555405573e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.207714059557918e-06</v>
+        <v>-3.274671555405573e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3341,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.343061484408163e-06</v>
+        <v>1.371096412738963e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.343061484408163e-06</v>
+        <v>1.371096412738963e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.302801913331631e-07</v>
+        <v>-4.583151196639627e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.937240411694252e-07</v>
+        <v>1.97767817030164e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.937240411694252e-07</v>
+        <v>1.97767817030164e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.937240411694252e-07</v>
+        <v>-1.97767817030164e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7640168.688929425</v>
+        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7646133.453841745</v>
+        <v>7809380.680484595</v>
       </c>
     </row>
     <row r="28">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7640168.688929425</v>
+        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="32">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2671332.408489357</v>
+        <v>-2508085.181846506</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>10275116.67221771</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1396229.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>11671346.48221771</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>7803415.915572274</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>5964.764912320331</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>7809380.680484595</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>7803415.915572274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7803415.915572274</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2508085.181846506</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>10311501.09741878</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>180470.6204848008</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>10152205.00022014</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10152205.00022014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-7803415.915572274</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>1036939.902582951</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-01 → 2026-03-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=447736930, avalanche_c=81789468, base=44106126, ethereum=24781026, optimism=149701411, unichain=44253240</t>
+          <t>2026-03-01 → 2026-03-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:42:52+00:00</t>
+          <t>arbitrum=447736930, avalanche_c=81789468, base=44106126, ethereum=24781026, optimism=149701411, unichain=44253240</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:33:45+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1396229.81</v>
+        <v>1412270.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11671346.48221771</v>
+        <v>11687387.49221771</v>
       </c>
     </row>
     <row r="9">

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10152205.00022014</v>
+        <v>10152205.00021997</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11687387.49221771</v>
+        <v>11687387.49221754</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7803415.915572274</v>
+        <v>7801904.956334603</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5964.764912320331</v>
+        <v>5979.891007520028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>7809380.680484595</v>
+        <v>7807884.847342123</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7803415.915572274</v>
+        <v>7801904.956334603</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2508085.181846506</v>
+        <v>-2509596.141084177</v>
       </c>
     </row>
     <row r="17">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10152205.00022014</v>
+        <v>10152205.00021997</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-7803415.915572274</v>
+        <v>-7801904.956334603</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1036939.902582951</v>
+        <v>1038450.861820448</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:33:45+00:00</t>
+          <t>2026-07-07T00:08:18+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>572733555.2197744</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1802372.703376638</v>
+        <v>1802372.703376585</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1802372.703376638</v>
+        <v>1802372.703376585</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2540242.205247048</v>
+        <v>2539761.461638205</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2540242.205247048</v>
+        <v>2539761.461638205</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-737869.5018704099</v>
+        <v>-737388.7582616191</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -920,13 +920,13 @@
         <v>27806689.150438</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2659819</v>
+        <v>2659819.000000003</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2659819</v>
+        <v>2659819.000000003</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1396138.384446995</v>
+        <v>1395874.163734499</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1396138.384446995</v>
+        <v>1395874.163734499</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1263680.615553005</v>
+        <v>1263944.836265505</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>879993.8786813826</v>
+        <v>879827.3388797356</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>879993.8786813826</v>
+        <v>879827.3388797356</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-304763.1816193826</v>
+        <v>-304596.6418177356</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>613567.4144554521</v>
+        <v>613451.2961528412</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>613567.4144554521</v>
+        <v>613451.2961528412</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-9020.694584773077</v>
+        <v>-8904.576282162108</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>449845.3381828347</v>
+        <v>449760.2044617854</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>449845.3381828347</v>
+        <v>449760.2044617854</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>120484.2366703383</v>
+        <v>120569.3703913877</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>399228.6965259673</v>
+        <v>399153.1420595762</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>360763.5322179346</v>
+        <v>360687.9777515435</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>90109.39614633274</v>
+        <v>90184.9506127239</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>288993.7002569484</v>
+        <v>288939.0078838717</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>288993.7002569484</v>
+        <v>288939.0078838717</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>126101.3054441722</v>
+        <v>126155.9978172489</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>264056.4265121482</v>
+        <v>264006.4535453353</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>264056.4265121482</v>
+        <v>264006.4535453353</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-254673.7080647675</v>
+        <v>-254623.7350979545</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>264049.702122492</v>
+        <v>263999.730428277</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>264049.702122492</v>
+        <v>263999.730428277</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-192590.2554744919</v>
+        <v>-192540.283780277</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>267782.9450753636</v>
+        <v>267732.2668608468</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>241982.4075116948</v>
+        <v>241931.7292971779</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>55611.96372950323</v>
+        <v>55662.64194402007</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198848.4398392941</v>
+        <v>198810.8075551033</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>179689.6519631402</v>
+        <v>179652.0196789494</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>41295.95415756934</v>
+        <v>41333.5864417601</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1578,31 +1578,31 @@
         <v>45001420.37224875</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>172403.0735875274</v>
+        <v>172403.0735875621</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>172403.0735875274</v>
+        <v>172403.0735875621</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>54328358.31940126</v>
+        <v>54328358.31940125</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>143457.0771225184</v>
+        <v>143429.9277141558</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>143457.0771225184</v>
+        <v>143429.9277141558</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>28945.996465009</v>
+        <v>28973.1458734063</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>122554.2226197703</v>
+        <v>122531.0290994282</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>122554.2226197703</v>
+        <v>122531.0290994282</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-122554.2226197703</v>
+        <v>-122531.0290994282</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>42215.74933357976</v>
+        <v>42207.75995695939</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>42215.74933357976</v>
+        <v>42207.75995695939</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-42215.74933357976</v>
+        <v>-42207.75995695939</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26704.91852567672</v>
+        <v>26699.86459070966</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26704.91852567672</v>
+        <v>26699.86459070966</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>16835.99380160285</v>
+        <v>16841.04773656991</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>26404.29315598599</v>
+        <v>26399.29611469814</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>26404.29315598599</v>
+        <v>26399.29611469814</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-7093.882013985991</v>
+        <v>-7088.884972698137</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1964,13 +1964,13 @@
         <v>-10545.180597</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>1.2448e-10</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>3.225e-11</v>
+        <v>1.2448e-10</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13200.75542624058</v>
+        <v>13198.25716887364</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13200.75542624058</v>
+        <v>13198.25716887364</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13200.75542624055</v>
+        <v>-13198.25716887352</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2029,31 +2029,31 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>-7.09e-10</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>3.218e-09</v>
+        <v>-7.09e-10</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4991412.147209223</v>
+        <v>4991412.147209226</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13180.10371568246</v>
+        <v>13177.60936667428</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13180.10371568246</v>
+        <v>13177.60936667428</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13180.10371567924</v>
+        <v>-13177.60936667499</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2094,31 +2094,31 @@
         <v>-2224.277443</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>-7.873499999999999e-09</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.3225e-09</v>
+        <v>-7.873499999999999e-09</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4983312.81205645</v>
+        <v>4983312.812056454</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13158.7169669642</v>
+        <v>13156.22666542155</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13158.7169669642</v>
+        <v>13156.22666542155</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13158.71696696287</v>
+        <v>-13156.22666542942</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2159,31 +2159,31 @@
         <v>-541036.95825</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>3.9e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-1.663e-08</v>
+        <v>3.9e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4975726.070058748</v>
+        <v>4975726.070058744</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13138.68374922045</v>
+        <v>13136.1972389861</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13138.68374922045</v>
+        <v>13136.1972389861</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13138.68374923708</v>
+        <v>-13136.19723898571</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2293,31 +2293,31 @@
         <v>-493.9461983095568</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4849.497356413308</v>
+        <v>4849.497356367622</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4849.497356413308</v>
+        <v>4849.497356367622</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1717843.021793645</v>
+        <v>1717843.021793663</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4536.060843455039</v>
+        <v>4535.202388991448</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4536.060843455039</v>
+        <v>4535.202388991448</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>313.4365129582695</v>
+        <v>314.2949673761746</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2578.10267470959</v>
+        <v>2577.614765965594</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2329.705843899025</v>
+        <v>2329.217935155028</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>535.4088267142429</v>
+        <v>535.8967354582393</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2395,12 +2395,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2410,67 +2410,71 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>12.69155787858941</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3.480000000005129</v>
+        <v>12.69155787858941</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3.480000000005129</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>12.69155787858941</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>2580.581437997849</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>6.814170017716019</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.814170017716019</v>
+        <v>12.69155787858941</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-3.33417001771089</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2479,40 +2483,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-66.81783951655405</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.29454480160933</v>
+        <v>3.480000000005129</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.29454480160933</v>
+        <v>3.480000000005129</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>458.062434320099</v>
+        <v>2580.581437997849</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.209539548036008</v>
+        <v>6.812880428605649</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.209539548036008</v>
+        <v>6.812880428605649</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.08500525357332127</v>
+        <v>-3.33288042860052</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2525,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2540,62 +2544,66 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>15.02635028417003</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>345.4148236875836</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.9120872143731815</v>
+        <v>0</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9120872143731815</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.04134929538547594</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="R28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2609,40 +2617,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>-66.81783951655405</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>1.294544801609128</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>1.294544801609128</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>458.0624343200989</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7496466078419327</v>
+        <v>1.209310641356889</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7496466078419327</v>
+        <v>1.209310641356889</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7496466078419327</v>
+        <v>0.08523416025223907</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,59 +2663,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>10.263802</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>10.263802</v>
+        <v>15.02635028417003</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-2.0038e-09</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-2.0038e-09</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>220.7452180964028</v>
+        <v>345.4148236875836</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.5828901287741283</v>
+        <v>0.9119146008727397</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5828901287741283</v>
+        <v>0.9119146008727397</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.5828901307779283</v>
+        <v>0.04152190888591774</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2720,17 +2728,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2739,40 +2747,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.2885977772774213</v>
+        <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2611016613043888</v>
+        <v>0.7495047364035058</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2611016613043888</v>
+        <v>0.7495047364035058</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.02749611597303243</v>
+        <v>-0.7495047364035058</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,17 +2793,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2804,40 +2812,40 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1868.74164</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
+        <v>10.263802</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-1868.74164</v>
+        <v>10.263802</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-5.583040730011e-08</v>
+        <v>-1.870482e-08</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-5.583040730011e-08</v>
+        <v>-1.870482e-08</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>49.19685112472924</v>
+        <v>220.7452181171656</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1299070445768462</v>
+        <v>0.5827798162361175</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1299070445768462</v>
+        <v>0.5827798162361175</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.1299071004072535</v>
+        <v>-0.5827798349409374</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2850,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2869,40 +2877,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>0.2885977772774213</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05784559208426222</v>
+        <v>0.2610522475301152</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05784559208426222</v>
+        <v>0.2610522475301152</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.0578395398778121</v>
+        <v>0.02754552974730608</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2915,12 +2923,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2930,44 +2938,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1.210594</v>
+        <v>1868.74164</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>133501.211399</v>
+        <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>133500.000805</v>
+        <v>-1868.74164</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>133500.000805</v>
+        <v>-9.778202630006999e-08</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>133500.000805</v>
+        <v>-9.778202630006999e-08</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>1.210594</v>
+        <v>49.19685105012429</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.003196641352588766</v>
+        <v>0.1298824593299653</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.003196641352588766</v>
+        <v>0.1298824593299653</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>133499.9976083587</v>
+        <v>-0.1298825571119916</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2995,44 +3003,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057463</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.05756</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>9.7e-05</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057463</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001517342742850272</v>
+        <v>0.05783464474284855</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001517342742850272</v>
+        <v>0.05783464474284855</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-5.473427428502721e-05</v>
+        <v>-0.05782859253639842</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3045,59 +3053,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.006319</v>
+        <v>1.210594</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006327</v>
+        <v>133501.211399</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>8e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>8e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>8e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.006319</v>
+        <v>1.210594</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.668567389810986e-05</v>
+        <v>0.003196036384725131</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.668567389810986e-05</v>
+        <v>0.003196036384725131</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-8.685673898109861e-06</v>
+        <v>133499.9976089636</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,12 +3118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3129,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>0.057463</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>0.05756</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>9.7e-05</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>9.7e-05</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>4.802837190430001e-07</v>
+        <v>9.7e-05</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>0.057463</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.515863068762813e-05</v>
+        <v>0.0001517055584080709</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.515863068762813e-05</v>
+        <v>0.0001517055584080709</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.467834696858513e-05</v>
+        <v>-5.470555840807093e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.001692</v>
+        <v>0.006319</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001696</v>
+        <v>0.006327</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>4e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.001692</v>
+        <v>0.006319</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>4.467820895015332e-06</v>
+        <v>1.668251611611994e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>4.467820895015332e-06</v>
+        <v>1.668251611611994e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-4.678208950153324e-07</v>
+        <v>-8.682516116119942e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3255,44 +3263,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>4.802837190430001e-07</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.274671555405573e-06</v>
+        <v>1.515576190023186e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.274671555405573e-06</v>
+        <v>1.515576190023186e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.274671555405573e-06</v>
+        <v>-1.467547818118886e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,17 +3313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3324,40 +3332,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0.001692</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.001696</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>9.12781293076e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0.001692</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.371096412738963e-06</v>
+        <v>4.466975355036389e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.371096412738963e-06</v>
+        <v>4.466975355036389e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.583151196639627e-07</v>
+        <v>-4.66975355036389e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3385,14 +3393,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3410,19 +3418,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.97767817030164e-07</v>
+        <v>3.274051820240921e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.97767817030164e-07</v>
+        <v>3.274051820240921e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.97767817030164e-07</v>
+        <v>-3.274051820240921e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,44 +3458,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>9.12781293076e-07</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>9.12781293075e-07</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>9.12781293075e-07</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1.370836931246934e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1.370836931246934e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>-4.580556381719338e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,14 +3523,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3540,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>1.977303892550188e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>1.977303892550188e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0</v>
+        <v>-1.977303892550188e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3608,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3625,21 +3633,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3699,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3727,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3742,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3751,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>805478.9999998595</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3759,17 +3763,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3779,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3792,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3816,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>1.16184e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3829,12 +3837,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3857,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>805478.9999999489</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>805478.9999999489</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
@@ -3872,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3881,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>6.37405e-09</v>
+        <v>805478.9999999489</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3889,26 +3897,22 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3917,31 +3921,31 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>1.4613665e-07</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>1.4613665e-07</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3950,39 +3954,35 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0</v>
+        <v>1.4613665e-07</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7726355e-07</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7726355e-07</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>1.886069370967742e-07</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7726355e-07</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4027,22 +4027,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>287780830.420175</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>456780102.344065</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>387977397.421864</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>867900893.337617</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>94443.720094</v>
+        <v>287780830.420175</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>504861.558051</v>
+        <v>456780102.344065</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>387977397.421864</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>94443.720094</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>152857139.195815</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>73619968.24222299</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2431714480.2962</v>
+        <v>2431274483.082148</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1431714480.2962</v>
+        <v>1431274483.082148</v>
       </c>
     </row>
     <row r="8">
@@ -4543,7 +4681,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.04124672584310142</v>
+        <v>0.04124672351396398</v>
       </c>
     </row>
     <row r="9">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03941483592081255</v>
+        <v>0.03941450206741989</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-18.31889922288867</v>
+        <v>-18.32221446544094</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8348004.6733626</v>
+        <v>8346493.714124929</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7983886.536057075</v>
+        <v>7982375.576819404</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1431714480.2962</v>
+        <v>1431274483.082148</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4913984.332756353</v>
+        <v>4912473.373518681</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7803415.915572274</v>
+        <v>7801904.956334603</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5964.764912320331</v>
+        <v>5979.891007520028</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7809380.680484595</v>
+        <v>7807884.847342123</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7803415.915572274</v>
+        <v>7801904.956334603</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2508085.181846506</v>
+        <v>-2509596.141084177</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>5964.764912320331</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.434537321108676</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.434537321108676</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>12.69155787858941</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>12.69155787858941</v>
       </c>
     </row>
   </sheetData>
@@ -5174,16 +5392,16 @@
         <v>105883906.3657945</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>68336335.76099491</v>
+        <v>68609743.58805992</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>46518715.05860327</v>
+        <v>46685301.33685334</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>159029980.3263338</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2558447690.725616</v>
+        <v>2558007696.6203</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5201,7 +5419,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>279700.6628648615</v>
+        <v>279649.7698130184</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>362372.7836082564</v>
@@ -5223,16 +5441,16 @@
         <v>105819063.6808732</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>61915033.21617521</v>
+        <v>62180265.14471421</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>55094509.141181</v>
+        <v>55269271.23447712</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>168986345.7344508</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2586120863.499631</v>
+        <v>2585680869.477796</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5250,7 +5468,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>282901.5516941324</v>
+        <v>282850.6586519453</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>366967.0057137655</v>
@@ -5272,16 +5490,16 @@
         <v>106380840.4381838</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>62816547.65419868</v>
+        <v>63092546.17374469</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>42689471.90948798</v>
+        <v>42853467.77357857</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>168969242.5220673</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2573061893.578585</v>
+        <v>2572621899.194949</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5299,7 +5517,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>281391.0522915734</v>
+        <v>281340.1592075377</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>364188.9227772035</v>
@@ -5321,16 +5539,16 @@
         <v>106454430.4482588</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>53142917.37872301</v>
+        <v>53391032.12136601</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>55911480.50712221</v>
+        <v>56103361.97358591</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>115233339.1487748</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2346160283.968735</v>
+        <v>2345720287.759628</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5348,7 +5566,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>255145.8930004883</v>
+        <v>255094.9997053048</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>332147.2060702533</v>
@@ -5370,16 +5588,16 @@
         <v>106526378.8617726</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>57673772.47965179</v>
+        <v>57937831.48920679</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>49361724.53585335</v>
+        <v>49537660.03372651</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>106666507.8312684</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2279081751.787829</v>
+        <v>2278641757.280401</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5397,7 +5615,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>247387.0817468918</v>
+        <v>247336.1886485374</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>323172.2909274696</v>
@@ -5419,16 +5637,16 @@
         <v>106682515.9973453</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>69545120.86060463</v>
+        <v>69818636.31013063</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>46486748.67527746</v>
+        <v>46653227.32908139</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>106913226.5360041</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2242230248.837922</v>
+        <v>2241790254.734592</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5446,7 +5664,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>243124.5577097146</v>
+        <v>243073.6646581012</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>319996.9528558906</v>
@@ -5468,16 +5686,16 @@
         <v>107681253.2199611</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>73529249.4886039</v>
+        <v>73802643.74943691</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>46912421.31784251</v>
+        <v>47079021.09366943</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>106954288.9193721</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2244371035.370409</v>
+        <v>2243931041.333749</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5495,7 +5713,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>243372.1772997648</v>
+        <v>243321.284255863</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>320874.9145723091</v>
@@ -5517,16 +5735,16 @@
         <v>107010807.4831251</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75438252.07703087</v>
+        <v>75719331.31069086</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>44344179.96811678</v>
+        <v>44503095.06236462</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>106935113.0757522</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2237207854.316899</v>
+        <v>2236767859.988991</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -5544,7 +5762,7 @@
         <v>0.03696000015803837</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>242543.6295071621</v>
+        <v>242492.7364295723</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>319890.3473729173</v>
@@ -5566,16 +5784,16 @@
         <v>107600220.1741485</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>58260508.43635895</v>
+        <v>58522232.32287996</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>48340039.58074408</v>
+        <v>48518309.9896852</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>107322066.296092</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2262837774.270913</v>
+        <v>2262397779.975451</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5593,7 +5811,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>236628.1463111601</v>
+        <v>236580.1547994352</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>308233.8100403404</v>
@@ -5615,16 +5833,16 @@
         <v>107794492.5793762</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>58215579.70095983</v>
+        <v>58481054.65838683</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>45805751.94094924</v>
+        <v>45980271.39919786</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>107333348.9757696</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2265355654.335234</v>
+        <v>2264915659.919558</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5642,7 +5860,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>236902.7791231647</v>
+        <v>236854.7875983278</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>308249.5404192483</v>
@@ -5664,16 +5882,16 @@
         <v>107856454.6880254</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>56297150.14197122</v>
+        <v>56578032.37202822</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>35005366.32205565</v>
+        <v>35164479.28108363</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>107387902.5867912</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2274956305.945729</v>
+        <v>2274516310.756644</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5691,7 +5909,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>237949.9513003584</v>
+        <v>237901.9596911633</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>307922.1415884829</v>
@@ -5713,16 +5931,16 @@
         <v>107835026.8157272</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>58937195.19455917</v>
+        <v>59203655.34857217</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48424749.6596028</v>
+        <v>48598283.90226091</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>106417723.4543805</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2257345895.285266</v>
+        <v>2256905900.888595</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5740,7 +5958,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>236029.130420614</v>
+        <v>235981.1388978499</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>307644.8136679553</v>
@@ -5762,16 +5980,16 @@
         <v>107856890.2413078</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>53758642.74291529</v>
+        <v>54020060.21808929</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>43642467.25609321</v>
+        <v>43821045.62793529</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>106551417.0948813</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2270954160.679399</v>
+        <v>2270514164.832382</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5789,7 +6007,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>237513.4251829637</v>
+        <v>237465.4335020061</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>308059.6170554543</v>
@@ -5811,16 +6029,16 @@
         <v>107952777.8445753</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>54628413.79015067</v>
+        <v>54890368.89710067</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>45214622.45488715</v>
+        <v>45392662.81697104</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>106911070.5772904</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2280232864.341573</v>
+        <v>2279792868.872539</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5838,7 +6056,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>238525.4815213931</v>
+        <v>238477.4898816631</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>309387.7089399265</v>
@@ -5860,16 +6078,16 @@
         <v>108076031.9837475</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>54000493.30115246</v>
+        <v>54259994.29568046</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>45329448.55387111</v>
+        <v>45509943.33997048</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>106936208.3821319</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2287358585.005143</v>
+        <v>2286918589.224516</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5887,7 +6105,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>239302.7054770241</v>
+        <v>239254.7138033077</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>310125.1536941137</v>
@@ -5909,16 +6127,16 @@
         <v>108275019.6506317</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>57421435.15917984</v>
+        <v>57690382.42227984</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>42079222.01166449</v>
+        <v>42250269.42528031</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>107032449.9192543</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2297837824.963365</v>
+        <v>2297397830.286649</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5936,7 +6154,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>240445.7079488969</v>
+        <v>240397.7163955875</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>311318.9781473554</v>
@@ -5958,16 +6176,16 @@
         <v>108480824.027681</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>52467553.34594446</v>
+        <v>52717256.17130646</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>46320240.07094195</v>
+        <v>46510535.17050985</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>107504855.7115974</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2298952454.331382</v>
+        <v>2298512456.406452</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5985,7 +6203,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>240567.2839532584</v>
+        <v>240519.2920456564</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>311436.7743801901</v>
@@ -6007,16 +6225,16 @@
         <v>108579051.0268968</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>56498201.94699442</v>
+        <v>56769121.27752043</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>40663062.32367405</v>
+        <v>40832137.52072863</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>107436888.0729907</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2390700622.690355</v>
+        <v>2390260628.162775</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6034,7 +6252,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>250574.5348266227</v>
+        <v>250526.5432895799</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>321269.9152686698</v>
@@ -6056,16 +6274,16 @@
         <v>108377058.0866341</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>61287940.00011939</v>
+        <v>61562101.53902039</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>46108021.12238023</v>
+        <v>46273853.74622926</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>107184053.179774</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2379149135.906709</v>
+        <v>2378709141.743959</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6083,7 +6301,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>249314.579142799</v>
+        <v>249266.5876455494</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>321076.6795480434</v>
@@ -6105,16 +6323,16 @@
         <v>108287715.446821</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>84447370.91364799</v>
+        <v>84731364.744739</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>56111545.25512103</v>
+        <v>56267546.52349077</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>107194547.5382319</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2355227244.167172</v>
+        <v>2354787249.067712</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6132,7 +6350,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>246705.3458874128</v>
+        <v>246657.3542879933</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>322076.0301177018</v>
@@ -6154,16 +6372,16 @@
         <v>108621267.8684392</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>83886845.5979041</v>
+        <v>84150471.91215311</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>64911091.2139782</v>
+        <v>65087459.91658953</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>107211163.3616333</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2517373473.29451</v>
+        <v>2516933478.277649</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6181,7 +6399,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>264391.1266726874</v>
+        <v>264343.1350822774</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>340698.6597746177</v>
@@ -6203,16 +6421,16 @@
         <v>108663588.8738396</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>82897801.95004173</v>
+        <v>83173507.79702972</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>53511159.10691563</v>
+        <v>53675447.63570868</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>107220548.4053871</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2592515142.794907</v>
+        <v>2592075148.419126</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6230,7 +6448,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>272587.0563700715</v>
+        <v>272539.0648495859</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>347548.926062625</v>
@@ -6252,16 +6470,16 @@
         <v>108701902.6320863</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>86422512.14540139</v>
+        <v>86716154.42197838</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>46634275.54346722</v>
+        <v>46780629.30083082</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>107244908.9822976</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2590435765.132995</v>
+        <v>2589995769.099054</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6279,7 +6497,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>272360.2523444934</v>
+        <v>272312.2606431474</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>346963.3264048395</v>
@@ -6301,16 +6519,16 @@
         <v>108751046.811058</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>87890264.99936663</v>
+        <v>88189793.45313863</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>49715414.4930896</v>
+        <v>49855884.38853588</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>108592021.8578287</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2568367775.148189</v>
+        <v>2567927776.798971</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6328,7 +6546,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>269953.2297739198</v>
+        <v>269905.2378200394</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>345204.7592439654</v>
@@ -6350,16 +6568,16 @@
         <v>108755446.1169963</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>86014890.37784478</v>
+        <v>86303872.78026079</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>48444881.26366401</v>
+        <v>48595894.60552943</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>107978396.0840361</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2553872399.914997</v>
+        <v>2553432404.170715</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6377,7 +6595,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>268372.1752519968</v>
+        <v>268324.1835822448</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>343214.1208375512</v>
@@ -6399,16 +6617,16 @@
         <v>108967111.5345911</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>88895924.8823521</v>
+        <v>89210294.50223809</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>46568078.51505661</v>
+        <v>46693711.48266955</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>112655549.2029514</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2566729738.730822</v>
+        <v>2566289736.143323</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6426,7 +6644,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>269774.5641758866</v>
+        <v>269726.5717597242</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>345259.2826226361</v>
@@ -6448,16 +6666,16 @@
         <v>109093717.1373149</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>89669597.74944127</v>
+        <v>89998145.86291027</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>46803310.00659268</v>
+        <v>46914770.62487348</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>112685017.5580367</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2561124086.876928</v>
+        <v>2560684078.145178</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6475,7 +6693,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>269163.1387336787</v>
+        <v>269115.1456473442</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>344774.924897235</v>
@@ -6497,16 +6715,16 @@
         <v>109074883.3027603</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>89370219.19929697</v>
+        <v>89688160.39976697</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47903347.44613171</v>
+        <v>48025411.35118448</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>112893900.0040528</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2544949854.542199</v>
+        <v>2544509849.436676</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6524,7 +6742,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>267398.9661779453</v>
+        <v>267350.9734871342</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>343118.8118121212</v>
@@ -6546,16 +6764,16 @@
         <v>109092111.8168385</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>89530342.68923661</v>
+        <v>89848531.62996262</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>49134306.49835142</v>
+        <v>49256122.71051931</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>112902235.561008</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2693383176.018544</v>
+        <v>2692943170.865651</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6573,7 +6791,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>283589.0385526734</v>
+        <v>283541.0458566954</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>359463.4021277596</v>
@@ -6595,16 +6813,16 @@
         <v>109138294.8517408</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>89401613.70311053</v>
+        <v>89704531.86731154</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>62089606.40613436</v>
+        <v>62226693.88791864</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>123415130.4064669</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>2706579711.643719</v>
+        <v>2706139705.997734</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6622,7 +6840,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>285028.4247008928</v>
+        <v>284980.4319511319</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>363453.5318884568</v>
@@ -6644,16 +6862,16 @@
         <v>109145503.3638819</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>89546424.48277703</v>
+        <v>89830501.58562304</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>75335921.8580665</v>
+        <v>75491854.16687198</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>125802289.7933941</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2800227621.076518</v>
+        <v>2799787611.664866</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6671,7 +6889,7 @@
         <v>0.03675104196384631</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>295242.8860925731</v>
+        <v>295194.8929320796</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>375389.7649814264</v>
@@ -6696,7 +6914,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>7983886.536057075</v>
+        <v>7982375.576819404</v>
       </c>
       <c r="O38" s="12" t="n">
         <v>10311501.09741878</v>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T00:08:18+00:00</t>
+          <t>2026-07-07T14:43:57+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10152205.00021997</v>
+        <v>10152205.00022022</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11687387.49221754</v>
+        <v>11687387.49221779</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10152205.00021997</v>
+        <v>10152205.00022022</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1038450.861820448</v>
+        <v>1038450.861820704</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T14:43:57+00:00</t>
+          <t>2026-07-10T11:09:43+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2539761.461638205</v>
+        <v>2539748.486884333</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2539761.461638205</v>
+        <v>2539748.486884333</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-737388.7582616191</v>
+        <v>-737375.7835077473</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1395874.163734499</v>
+        <v>1395867.032701138</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1395874.163734499</v>
+        <v>1395867.032701138</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1263944.836265505</v>
+        <v>1263951.967298865</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>879827.3388797356</v>
+        <v>879822.8441492878</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>879827.3388797356</v>
+        <v>879822.8441492878</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-304596.6418177356</v>
+        <v>-304592.1470872878</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>613451.2961528412</v>
+        <v>613448.1622445195</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>613451.2961528412</v>
+        <v>613448.1622445195</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-8904.576282162108</v>
+        <v>-8901.442373840344</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>449760.2044617854</v>
+        <v>449757.9067940546</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>449760.2044617854</v>
+        <v>449757.9067940546</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>120569.3703913877</v>
+        <v>120571.6680591185</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>399153.1420595762</v>
+        <v>399151.1029256443</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>360687.9777515435</v>
+        <v>360685.9386176115</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>90184.9506127239</v>
+        <v>90186.98974665582</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>288939.0078838717</v>
+        <v>288937.5317954406</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>288939.0078838717</v>
+        <v>288937.5317954406</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>126155.9978172489</v>
+        <v>126157.47390568</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>264006.4535453353</v>
+        <v>264005.1048286125</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>264006.4535453353</v>
+        <v>264005.1048286125</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-254623.7350979545</v>
+        <v>-254622.3863812317</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263999.730428277</v>
+        <v>263998.3817459003</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263999.730428277</v>
+        <v>263998.3817459003</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-192540.283780277</v>
+        <v>-192538.9350979003</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>267732.2668608468</v>
+        <v>267730.8991102456</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>241931.7292971779</v>
+        <v>241930.3615465767</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>55662.64194402007</v>
+        <v>55664.00969462127</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198810.8075551033</v>
+        <v>198809.7919001554</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>179652.0196789494</v>
+        <v>179651.0040240015</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>41333.5864417601</v>
+        <v>41334.60209670804</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>143429.9277141558</v>
+        <v>143429.1949807719</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>143429.9277141558</v>
+        <v>143429.1949807719</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>28973.1458734063</v>
+        <v>28973.87860679015</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>122531.0290994282</v>
+        <v>122530.4031312149</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>122531.0290994282</v>
+        <v>122530.4031312149</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-122531.0290994282</v>
+        <v>-122530.4031312149</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>42207.75995695939</v>
+        <v>42207.54433226188</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>42207.75995695939</v>
+        <v>42207.54433226188</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-42207.75995695939</v>
+        <v>-42207.54433226188</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26699.86459070966</v>
+        <v>26699.72819043085</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26699.86459070966</v>
+        <v>26699.72819043085</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>16841.04773656991</v>
+        <v>16841.18413684872</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>26399.29611469814</v>
+        <v>26399.16124991865</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>26399.29611469814</v>
+        <v>26399.16124991865</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-7088.884972698137</v>
+        <v>-7088.750107918649</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1936,17 +1936,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1955,40 +1955,40 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>5000000</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>5000000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-10545.180597</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1.2448e-10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.2448e-10</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>4999233.117450742</v>
+        <v>5000000</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13198.25716887364</v>
+        <v>13200.2143463952</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13198.25716887364</v>
+        <v>13200.2143463952</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13198.25716887352</v>
+        <v>-13200.2143463952</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2001,17 +2001,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2023,37 +2023,37 @@
         <v>5000000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>5000000</v>
+        <v>4997775.722557</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0</v>
+        <v>-2224.277443</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-7.09e-10</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-7.09e-10</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4991412.147209226</v>
+        <v>4999928.249114742</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13177.60936667428</v>
+        <v>13200.02492098221</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13177.60936667428</v>
+        <v>13200.02492098221</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13177.60936667499</v>
+        <v>-13200.02492098221</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2066,17 +2066,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2085,40 +2085,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>4997665.827264</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>4987120.646667</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-2224.277443</v>
+        <v>-10545.180597</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-7.873499999999999e-09</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-7.873499999999999e-09</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4983312.812056454</v>
+        <v>4997325.660147968</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13156.22666542155</v>
+        <v>13193.15397453882</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13156.22666542155</v>
+        <v>13193.15397453882</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13156.22666542942</v>
+        <v>-13193.15397453882</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2159,31 +2159,31 @@
         <v>-541036.95825</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3.9e-10</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3.9e-10</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4975726.070058744</v>
+        <v>4966337.792426161</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13136.1972389861</v>
+        <v>13111.3446753257</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13136.1972389861</v>
+        <v>13111.3446753257</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13136.19723898571</v>
+        <v>-13111.3446753257</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4535.202388991448</v>
+        <v>4535.179220227119</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4535.202388991448</v>
+        <v>4535.179220227119</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>314.2949673761746</v>
+        <v>314.3181361405034</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2577.614765965594</v>
+        <v>2577.601597832416</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2329.217935155028</v>
+        <v>2329.204767021852</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>535.8967354582393</v>
+        <v>535.9099035914163</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>6.812880428605649</v>
+        <v>6.812845623980074</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>6.812880428605649</v>
+        <v>6.812845623980074</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-3.33288042860052</v>
+        <v>-3.332845623974946</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2529,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,20 +2544,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>220000.0301712902</v>
+        <v>1868.74164</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>220002.4647086113</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2.434537321108676</v>
+        <v>-1868.74164</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2.434537321108676</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
@@ -2566,114 +2566,114 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2.434537321108676</v>
+        <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>220000.0301712902</v>
+        <v>1808.459651612903</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0</v>
+        <v>4.774411007619504</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.434537321108676</v>
+        <v>4.774411007619504</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0</v>
+        <v>-4.774411007619504</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>220000.0301712902</v>
+        <v>0</v>
       </c>
       <c r="R28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-66.81783951655405</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1.294544801609128</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.294544801609128</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>458.0624343200989</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1.209310641356889</v>
+        <v>0</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.209310641356889</v>
+        <v>2.434537321108676</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.08523416025223907</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="R29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>15.02635028417003</v>
+        <v>-66.81783951655405</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>1.294544801609128</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.9534365097586575</v>
+        <v>1.294544801609128</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>345.4148236875836</v>
+        <v>458.0624343200989</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.9119146008727397</v>
+        <v>1.209304463411376</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.9119146008727397</v>
+        <v>1.209304463411376</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.04152190888591774</v>
+        <v>0.08524033819775212</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2728,17 +2728,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0</v>
+        <v>15.02635028417003</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0</v>
+        <v>0.9534365097586575</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>345.4148236875836</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.7495047364035058</v>
+        <v>0.9119099422196822</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7495047364035058</v>
+        <v>0.9119099422196822</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.7495047364035058</v>
+        <v>0.04152656753897518</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2793,59 +2793,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>10.263802</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10.263802</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-1.870482e-08</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-1.870482e-08</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>220.7452181171656</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.5827798162361175</v>
+        <v>0.7495009074456972</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.5827798162361175</v>
+        <v>0.7495009074456972</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.5827798349409374</v>
+        <v>-0.7495009074456972</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2610522475301152</v>
+        <v>0.2610509139053986</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2610522475301152</v>
+        <v>0.2610509139053986</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.02754552974730608</v>
+        <v>0.02754686337202264</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2923,12 +2923,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2938,44 +2938,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1868.74164</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-1868.74164</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-9.778202630006999e-08</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-9.778202630006999e-08</v>
+        <v>6.052206450123245e-06</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>49.19685105012429</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1298824593299653</v>
+        <v>0.05783434928585696</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1298824593299653</v>
+        <v>0.05783434928585696</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.1298825571119916</v>
+        <v>-0.05782829707940684</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2988,12 +2988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3003,44 +3003,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>1.210594</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>133501.211399</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>6.052206450123245e-06</v>
+        <v>133500.000805</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>1.210594</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05783464474284855</v>
+        <v>0.003196020057291991</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05783464474284855</v>
+        <v>0.003196020057291991</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05782859253639842</v>
+        <v>133499.9976089799</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3053,59 +3053,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1.210594</v>
+        <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>133501.211399</v>
+        <v>10.263802</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>133500.000805</v>
+        <v>10.263802</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>133500.000805</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>133500.000805</v>
+        <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>1.210594</v>
+        <v>0.3310903870967742</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.003196036384725131</v>
+        <v>0.000874092815541676</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.003196036384725131</v>
+        <v>0.000874092815541676</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>133499.9976089636</v>
+        <v>-0.000874092815541676</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001517055584080709</v>
+        <v>0.0001517047833973815</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001517055584080709</v>
+        <v>0.0001517047833973815</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-5.470555840807093e-05</v>
+        <v>-5.470478339738152e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.668251611611994e-05</v>
+        <v>1.668243089097426e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.668251611611994e-05</v>
+        <v>1.668243089097426e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-8.682516116119942e-06</v>
+        <v>-8.682430890974259e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.515576190023186e-05</v>
+        <v>1.515568447473999e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.515576190023186e-05</v>
+        <v>1.515568447473999e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.467547818118886e-05</v>
+        <v>-1.467540075569699e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>4.466975355036389e-06</v>
+        <v>4.466952534820137e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>4.466975355036389e-06</v>
+        <v>4.466952534820137e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.66975355036389e-07</v>
+        <v>-4.66952534820137e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>3.274051820240921e-06</v>
+        <v>3.274035094254181e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>3.274051820240921e-06</v>
+        <v>3.274035094254181e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.274051820240921e-06</v>
+        <v>-3.274035094254181e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.370836931246934e-06</v>
+        <v>1.370829928120046e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.370836931246934e-06</v>
+        <v>1.370829928120046e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.580556381719338e-07</v>
+        <v>-4.580486350450457e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.977303892550188e-07</v>
+        <v>1.977293791195505e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.977303892550188e-07</v>
+        <v>1.977293791195505e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.977303892550188e-07</v>
+        <v>-1.977293791195505e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3930,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1.4613665e-07</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.4613665e-07</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>1.4613665e-07</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
         <v>0</v>
@@ -3995,19 +3995,19 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-2.7726355e-07</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-2.7726355e-07</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>1.886069370967742e-07</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>-2.7726355e-07</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10152205.00022022</v>
+        <v>10347147.38174922</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11687387.49221779</v>
+        <v>11882329.87374679</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10152205.00022022</v>
+        <v>10347147.38174922</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1038450.861820704</v>
+        <v>1233393.243349704</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:09:43+00:00</t>
+          <t>2026-07-13T18:25:28+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2539748.486884333</v>
+        <v>2487027.81142366</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2539748.486884333</v>
+        <v>2487027.81142366</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-737375.7835077473</v>
+        <v>-684655.1080470749</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1395867.032701138</v>
+        <v>1366891.30805859</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1395867.032701138</v>
+        <v>1366891.30805859</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1263951.967298865</v>
+        <v>1292927.691941413</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>879822.8441492878</v>
+        <v>861559.2818836465</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>879822.8441492878</v>
+        <v>861559.2818836465</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-304592.1470872878</v>
+        <v>-286328.5848216465</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>613448.1622445195</v>
+        <v>600714.0660768653</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>613448.1622445195</v>
+        <v>600714.0660768653</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-8901.442373840344</v>
+        <v>3832.653793813822</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>449757.9067940546</v>
+        <v>440421.7300968695</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>449757.9067940546</v>
+        <v>440421.7300968695</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>120571.6680591185</v>
+        <v>129907.8447563036</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>399151.1029256443</v>
+        <v>390865.4337478558</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>360685.9386176115</v>
+        <v>352400.2694398231</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>90186.98974665582</v>
+        <v>98472.65892444426</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1225,12 +1225,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1240,44 +1240,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>200002600.606636</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>495610843.871423</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-100000441.3465193</v>
+        <v>495610843.871423</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>415095.0057011207</v>
+        <v>162936.926398</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>415095.0057011207</v>
+        <v>162936.926398</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>109444257.5753876</v>
+        <v>116353783.7381843</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>288937.5317954406</v>
+        <v>300802.4861544512</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>288937.5317954406</v>
+        <v>300802.4861544512</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>126157.47390568</v>
+        <v>-137865.5597564511</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1290,12 +1290,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1305,44 +1305,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>100000617.7417743</v>
+        <v>200002600.606636</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-163.2954034076501</v>
+        <v>-100000441.3465193</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>9382.718447380783</v>
+        <v>415095.0057011207</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>9382.718447380783</v>
+        <v>415095.0057011207</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>100000309.8058436</v>
+        <v>109444257.5753876</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>264005.1048286125</v>
+        <v>282939.700939015</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>264005.1048286125</v>
+        <v>282939.700939015</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-254622.3863812317</v>
+        <v>132155.3047621056</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1355,12 +1355,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1370,44 +1370,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>100000062.958447</v>
+        <v>100000617.7417743</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>167.708442</v>
+        <v>-163.2954034076501</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>71459.446648</v>
+        <v>9382.718447380783</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>71459.446648</v>
+        <v>9382.718447380783</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>99997763.22495648</v>
+        <v>100000309.8058436</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263998.3817459003</v>
+        <v>258524.8269493234</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263998.3817459003</v>
+        <v>258524.8269493234</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-192538.9350979003</v>
+        <v>-249142.1085019426</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1420,82 +1420,82 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>101411572.6019855</v>
+        <v>100000062.958447</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100000230.666889</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>323394.9088048668</v>
+        <v>167.708442</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>323394.9088048668</v>
+        <v>71459.446648</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>323394.9088048668</v>
+        <v>71459.446648</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>101411572.6019855</v>
+        <v>99997763.22495648</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>267730.8991102456</v>
+        <v>258518.2434258879</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>241930.3615465767</v>
+        <v>258518.2434258879</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>55664.00969462127</v>
+        <v>-187058.7967778879</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>25800.53756366883</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1504,63 +1504,63 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>75305516.51778577</v>
+        <v>101411572.6019855</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>240144.3939968634</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>240144.3939968634</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>240144.3939968634</v>
+        <v>323394.9088048668</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>75305516.51778577</v>
+        <v>101411572.6019855</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198809.7919001554</v>
+        <v>262173.2803477275</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>179651.0040240015</v>
+        <v>236372.7427840586</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>41334.60209670804</v>
+        <v>61221.62845713936</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>19158.78787615384</v>
+        <v>25800.53756366883</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1569,58 +1569,58 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>55000541.20928549</v>
+        <v>75305516.51778577</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>45001420.37224875</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>172403.0735875621</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>172403.0735875621</v>
+        <v>240144.3939968634</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>54328358.31940125</v>
+        <v>75305516.51778577</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>143429.1949807719</v>
+        <v>194682.8531220443</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>143429.1949807719</v>
+        <v>175524.0652458904</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>28973.87860679015</v>
+        <v>45461.54087481913</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>19158.78787615384</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1630,44 +1630,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>47958113.065451</v>
+        <v>55000541.20928549</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>37220.756204</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-47920892.309247</v>
+        <v>45001420.37224875</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>172403.0735875621</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>172403.0735875621</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>46412277.82966884</v>
+        <v>54328358.31940125</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>122530.4031312149</v>
+        <v>140451.8592015731</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>122530.4031312149</v>
+        <v>140451.8592015731</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-122530.4031312149</v>
+        <v>31951.21438598897</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1741,12 +1741,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1760,40 +1760,40 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>47958113.065451</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>37220.756204</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>-47920892.309247</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>32005.45513</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>32005.45513</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>15987446.57649752</v>
+        <v>10140549.70246165</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>42207.54433226188</v>
+        <v>26215.75735205086</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>42207.54433226188</v>
+        <v>26215.75735205086</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-42207.54433226188</v>
+        <v>5789.697777949136</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26699.72819043085</v>
+        <v>26145.48917342382</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26699.72819043085</v>
+        <v>26145.48917342382</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>16841.18413684872</v>
+        <v>17395.42315385575</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1899,31 +1899,31 @@
         <v>-20.869158</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19310.411142</v>
+        <v>19310.411143</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>19310.411142</v>
+        <v>19310.411143</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>9999519.915798903</v>
+        <v>9999519.915798871</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>26399.16124991865</v>
+        <v>25851.16146967328</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>26399.16124991865</v>
+        <v>25851.16146967328</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-7088.750107918649</v>
+        <v>-6540.750326673276</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13200.2143463952</v>
+        <v>12926.20130133918</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13200.2143463952</v>
+        <v>12926.20130133918</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13200.2143463952</v>
+        <v>-12926.20130133918</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13200.02492098221</v>
+        <v>12926.0158080619</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13200.02492098221</v>
+        <v>12926.0158080619</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13200.02492098221</v>
+        <v>-12926.0158080619</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13193.15397453882</v>
+        <v>12919.28749028406</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13193.15397453882</v>
+        <v>12919.28749028406</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13193.15397453882</v>
+        <v>-12919.28749028406</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13111.3446753257</v>
+        <v>12839.1764070698</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13111.3446753257</v>
+        <v>12839.1764070698</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13111.3446753257</v>
+        <v>-12839.1764070698</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4535.179220227119</v>
+        <v>4441.036940761133</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4535.179220227119</v>
+        <v>4441.036940761133</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>314.3181361405034</v>
+        <v>408.4604156064892</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2577.601597832416</v>
+        <v>2524.095158904307</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2329.204767021852</v>
+        <v>2275.698328093743</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>535.9099035914163</v>
+        <v>589.4163425195252</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>6.812845623980074</v>
+        <v>6.671423028411904</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>6.812845623980074</v>
+        <v>6.671423028411904</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-3.332845623974946</v>
+        <v>-3.191423028406775</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>4.774411007619504</v>
+        <v>4.67530270041962</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>4.774411007619504</v>
+        <v>4.67530270041962</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-4.774411007619504</v>
+        <v>-4.67530270041962</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1.209304463411376</v>
+        <v>1.184201446920611</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1.209304463411376</v>
+        <v>1.184201446920611</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08524033819775212</v>
+        <v>0.1103433546885175</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.9119099422196822</v>
+        <v>0.8929803086904571</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.9119099422196822</v>
+        <v>0.8929803086904571</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.04152656753897518</v>
+        <v>0.0604562010682003</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.7495009074456972</v>
+        <v>0.7339425975173788</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.7495009074456972</v>
+        <v>0.7339425975173788</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.7495009074456972</v>
+        <v>-0.7339425975173788</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2610509139053986</v>
+        <v>0.255631959791717</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2610509139053986</v>
+        <v>0.255631959791717</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.02754686337202264</v>
+        <v>0.03296581748570424</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05783434928585696</v>
+        <v>0.05663381073846745</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.05783434928585696</v>
+        <v>0.05663381073846745</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.05782829707940684</v>
+        <v>-0.05662775853201732</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.003196020057291991</v>
+        <v>0.00312967634763868</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.003196020057291991</v>
+        <v>0.00312967634763868</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>133499.9976089799</v>
+        <v>133499.9976753237</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.000874092815541676</v>
+        <v>0.0008559481985102429</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.000874092815541676</v>
+        <v>0.0008559481985102429</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-0.000874092815541676</v>
+        <v>-0.0008559481985102429</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001517047833973815</v>
+        <v>0.0001485556610757706</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001517047833973815</v>
+        <v>0.0001485556610757706</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-5.470478339738152e-05</v>
+        <v>-5.155566107577062e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.668243089097426e-05</v>
+        <v>1.633613320463245e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.668243089097426e-05</v>
+        <v>1.633613320463245e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-8.682430890974259e-06</v>
+        <v>-8.336133204632452e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.515568447473999e-05</v>
+        <v>1.484107933698585e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.515568447473999e-05</v>
+        <v>1.484107933698585e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.467540075569699e-05</v>
+        <v>-1.436079561794285e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>4.466952534820137e-06</v>
+        <v>4.374226520373177e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>4.466952534820137e-06</v>
+        <v>4.374226520373177e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.66952534820137e-07</v>
+        <v>-3.742265203731774e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>3.274035094254181e-06</v>
+        <v>3.206071930758895e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>3.274035094254181e-06</v>
+        <v>3.206071930758895e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.274035094254181e-06</v>
+        <v>-3.206071930758895e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3471,13 +3471,13 @@
         <v>9.12781293076e-07</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>9.12781293076e-07</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>9.12781293075e-07</v>
+        <v>9.12781293076e-07</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.370829928120046e-06</v>
+        <v>1.342373929376306e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.370829928120046e-06</v>
+        <v>1.342373929376306e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.580486350450457e-07</v>
+        <v>-4.295926363003065e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.977293791195505e-07</v>
+        <v>1.936248677951278e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.977293791195505e-07</v>
+        <v>1.936248677951278e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.977293791195505e-07</v>
+        <v>-1.936248677951278e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7801904.956334603</v>
+        <v>7860267.116630248</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>7807884.847342123</v>
+        <v>7866247.007637768</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7801904.956334603</v>
+        <v>7860267.116630248</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>10311501.09741878</v>
+        <v>10369863.25771442</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-7801904.956334603</v>
+        <v>-7860267.116630248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1233393.243349704</v>
+        <v>1175031.083054059</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13T18:25:28+00:00</t>
+          <t>2026-07-31T00:16:43+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2487027.81142366</v>
+        <v>2505211.410327668</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2487027.81142366</v>
+        <v>2505211.410327668</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-684655.1080470749</v>
+        <v>-702838.7069510828</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1366891.30805859</v>
+        <v>1376885.166260314</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1366891.30805859</v>
+        <v>1376885.166260314</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1292927.691941413</v>
+        <v>1282933.833739689</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>861559.2818836465</v>
+        <v>867858.4669357145</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>861559.2818836465</v>
+        <v>867858.4669357145</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-286328.5848216465</v>
+        <v>-292627.7698737145</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>600714.0660768653</v>
+        <v>605106.1133162907</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>600714.0660768653</v>
+        <v>605106.1133162907</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>3832.653793813822</v>
+        <v>-559.3934456115542</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>39014674.44036614</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>440421.7300968695</v>
+        <v>443641.8195755257</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>440421.7300968695</v>
+        <v>443641.8195755257</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>129907.8447563036</v>
+        <v>126687.7552776474</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>75936994.49835326</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>390865.4337478558</v>
+        <v>393723.198441948</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>352400.2694398231</v>
+        <v>355258.0341339153</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>98472.65892444426</v>
+        <v>95614.89423035199</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>300802.4861544512</v>
+        <v>303001.7666500037</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>300802.4861544512</v>
+        <v>303001.7666500037</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-137865.5597564511</v>
+        <v>-140064.8402520037</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>282939.700939015</v>
+        <v>285008.3798706551</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>282939.700939015</v>
+        <v>285008.3798706551</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>132155.3047621056</v>
+        <v>130086.6258304656</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>258524.8269493234</v>
+        <v>260414.999523342</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>258524.8269493234</v>
+        <v>260414.999523342</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-249142.1085019426</v>
+        <v>-251032.2810759612</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>258518.2434258879</v>
+        <v>260408.3678652821</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>258518.2434258879</v>
+        <v>260408.3678652821</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-187058.7967778879</v>
+        <v>-188948.9212172821</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>262173.2803477275</v>
+        <v>264090.1281414247</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>236372.7427840586</v>
+        <v>238289.5905777559</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>61221.62845713936</v>
+        <v>59304.78066344213</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>194682.8531220443</v>
+        <v>196106.2529322107</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>175524.0652458904</v>
+        <v>176947.4650560569</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>45461.54087481913</v>
+        <v>44038.14106465267</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>140451.8592015731</v>
+        <v>141478.7557490555</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>140451.8592015731</v>
+        <v>141478.7557490555</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>31951.21438598897</v>
+        <v>30924.31783850659</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>26215.75735205086</v>
+        <v>26407.43064756645</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>26215.75735205086</v>
+        <v>26407.43064756645</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>5789.697777949136</v>
+        <v>5598.02448243355</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26145.48917342382</v>
+        <v>26336.64871176709</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26145.48917342382</v>
+        <v>26336.64871176709</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>17395.42315385575</v>
+        <v>17204.26361551248</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>25851.16146967328</v>
+        <v>26040.16906709865</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>25851.16146967328</v>
+        <v>26040.16906709865</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-6540.750326673276</v>
+        <v>-6729.757924098654</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>12926.20130133918</v>
+        <v>13020.70963724776</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>12926.20130133918</v>
+        <v>13020.70963724776</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-12926.20130133918</v>
+        <v>-13020.70963724776</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12926.0158080619</v>
+        <v>13020.52278775913</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12926.0158080619</v>
+        <v>13020.52278775913</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12926.0158080619</v>
+        <v>-13020.52278775913</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12919.28749028406</v>
+        <v>13013.74527671083</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12919.28749028406</v>
+        <v>13013.74527671083</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12919.28749028406</v>
+        <v>-13013.74527671083</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12839.1764070698</v>
+        <v>12933.04847113422</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12839.1764070698</v>
+        <v>12933.04847113422</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12839.1764070698</v>
+        <v>-12933.04847113422</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>4441.036940761133</v>
+        <v>4473.507037829511</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>4441.036940761133</v>
+        <v>4473.507037829511</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>408.4604156064892</v>
+        <v>375.9903185381109</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2524.095158904307</v>
+        <v>2542.549771174522</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2275.698328093743</v>
+        <v>2294.152940363957</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>589.4163425195252</v>
+        <v>570.9617302493106</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>6.671423028411904</v>
+        <v>6.720200319888255</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>6.671423028411904</v>
+        <v>6.720200319888255</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-3.191423028406775</v>
+        <v>-3.240200319883126</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>4.67530270041962</v>
+        <v>4.709485602865971</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>4.67530270041962</v>
+        <v>4.709485602865971</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-4.67530270041962</v>
+        <v>-4.709485602865971</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1.184201446920611</v>
+        <v>1.192859590602576</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1.184201446920611</v>
+        <v>1.192859590602576</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1103433546885175</v>
+        <v>0.101685211006552</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.8929803086904571</v>
+        <v>0.8995092247274312</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.8929803086904571</v>
+        <v>0.8995092247274312</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.0604562010682003</v>
+        <v>0.05392728503122624</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.7339425975173788</v>
+        <v>0.7393087288290275</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.7339425975173788</v>
+        <v>0.7393087288290275</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.7339425975173788</v>
+        <v>-0.7393087288290275</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.255631959791717</v>
+        <v>0.2575009815222128</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.255631959791717</v>
+        <v>0.2575009815222128</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.03296581748570424</v>
+        <v>0.0310967957552085</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05663381073846745</v>
+        <v>0.05704788190170237</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.05663381073846745</v>
+        <v>0.05704788190170237</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.05662775853201732</v>
+        <v>-0.05704182969525224</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.00312967634763868</v>
+        <v>0.003152558592518863</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.00312967634763868</v>
+        <v>0.003152558592518863</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>133499.9976753237</v>
+        <v>133499.9976524414</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0008559481985102429</v>
+        <v>0.0008622063588142119</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0008559481985102429</v>
+        <v>0.0008622063588142119</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-0.0008559481985102429</v>
+        <v>-0.0008622063588142119</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001485556610757706</v>
+        <v>0.0001496418075770336</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001485556610757706</v>
+        <v>0.0001496418075770336</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-5.155566107577062e-05</v>
+        <v>-5.264180757703361e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.633613320463245e-05</v>
+        <v>1.645557283955372e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.633613320463245e-05</v>
+        <v>1.645557283955372e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-8.336133204632452e-06</v>
+        <v>-8.45557283955372e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.484107933698585e-05</v>
+        <v>1.494958806886522e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.484107933698585e-05</v>
+        <v>1.494958806886522e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.436079561794285e-05</v>
+        <v>-1.446930434982222e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>4.374226520373177e-06</v>
+        <v>4.406208141244642e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>4.374226520373177e-06</v>
+        <v>4.406208141244642e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-3.742265203731774e-07</v>
+        <v>-4.06208141244642e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>3.206071930758895e-06</v>
+        <v>3.229512732578053e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>3.206071930758895e-06</v>
+        <v>3.229512732578053e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.206071930758895e-06</v>
+        <v>-3.229512732578053e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.342373929376306e-06</v>
+        <v>1.352188531769918e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.342373929376306e-06</v>
+        <v>1.352188531769918e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.295926363003065e-07</v>
+        <v>-4.394072386939175e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.936248677951278e-07</v>
+        <v>1.950405322752981e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.936248677951278e-07</v>
+        <v>1.950405322752981e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.936248677951278e-07</v>
+        <v>-1.950405322752981e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.03717741935483871</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03680496665912168</v>
+        <v>0.03751760106772383</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03941450206741989</v>
+        <v>0.03970761352544775</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-18.32221446544094</v>
+        <v>-15.39109988516229</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>364118.1373055246</v>
+        <v>305755.9770098804</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7982375.576819404</v>
+        <v>8040737.737115049</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>364118.1373055246</v>
+        <v>305755.9770098804</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3069902.203300723</v>
+        <v>3128264.363596367</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7801904.956334603</v>
+        <v>7860267.116630248</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7807884.847342123</v>
+        <v>7866247.007637768</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10311501.09741878</v>
+        <v>10369863.25771442</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7801904.956334603</v>
+        <v>7860267.116630248</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>2</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.03723500015803836</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>279649.7698130184</v>
+        <v>280376.3165988637</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>362372.7836082564</v>
+        <v>363099.3303941016</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>2</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.0376933334913717</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>282850.6586519453</v>
+        <v>284787.6899648494</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>366967.0057137655</v>
+        <v>368904.0370266696</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>2</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.03760166682470503</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>281340.1592075377</v>
+        <v>283035.1362757938</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>364188.9227772035</v>
+        <v>365883.8998454597</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.03760166682470503</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>255094.9997053048</v>
+        <v>256789.976773561</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>332147.2060702533</v>
+        <v>333842.1831385095</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>2</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.03751000015803836</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>247336.1886485374</v>
+        <v>248789.0901454274</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>323172.2909274696</v>
+        <v>324625.1924243597</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>243073.6646581012</v>
+        <v>244284.4692533542</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>319996.9528558906</v>
+        <v>321207.7574511436</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>2</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>243321.284255863</v>
+        <v>244532.088851116</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>320874.9145723091</v>
+        <v>322085.7191675621</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>2</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03696000015803837</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>242492.7364295723</v>
+        <v>243703.5410248253</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>319890.3473729173</v>
+        <v>321101.1519681704</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>2</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>236580.1547994352</v>
+        <v>238275.4724503645</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>308233.8100403404</v>
+        <v>309929.1276912697</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>236854.7875983278</v>
+        <v>238550.1052492571</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>308249.5404192483</v>
+        <v>309944.8580701776</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>2</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>237901.9596911633</v>
+        <v>239597.2773420927</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>307922.1415884829</v>
+        <v>309617.4592394123</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>2</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>235981.1388978499</v>
+        <v>237918.5594138683</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>307644.8136679553</v>
+        <v>309582.2341839736</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>237465.4335020061</v>
+        <v>239402.8540180244</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>308059.6170554543</v>
+        <v>309997.0375714726</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>2</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>238477.4898816631</v>
+        <v>240414.9103976814</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>309387.7089399265</v>
+        <v>311325.1294559448</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>2</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>239254.7138033077</v>
+        <v>241192.1343193261</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>310125.1536941137</v>
+        <v>312062.574210132</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>2</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>240397.7163955875</v>
+        <v>242335.1369116058</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>311318.9781473554</v>
+        <v>313256.3986633738</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>2</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>240519.2920456564</v>
+        <v>242456.7125616747</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>311436.7743801901</v>
+        <v>313374.1948962084</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>2</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>250526.5432895799</v>
+        <v>252706.0453393061</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>321269.9152686698</v>
+        <v>323449.417318396</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>2</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>249266.5876455494</v>
+        <v>251446.0896952756</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>321076.6795480434</v>
+        <v>323256.1815977695</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0374</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>246657.3542879933</v>
+        <v>249078.916543821</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>322076.0301177018</v>
+        <v>324497.5923735294</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>2</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0374</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>264343.1350822774</v>
+        <v>266764.6973381051</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>340698.6597746177</v>
+        <v>343120.2220304454</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>2</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0374</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>272539.0648495859</v>
+        <v>274960.6271054136</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>347548.926062625</v>
+        <v>349970.4883184527</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>2</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0374</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>272312.2606431474</v>
+        <v>274733.822898975</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>346963.3264048395</v>
+        <v>349384.8886606672</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0374</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>269905.2378200394</v>
+        <v>272326.8000758671</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>345204.7592439654</v>
+        <v>347626.3214997931</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>2</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>268324.1835822448</v>
+        <v>270503.6856319709</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>343214.1208375512</v>
+        <v>345393.6228872773</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>2</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>269726.5717597242</v>
+        <v>271906.0738094503</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>345259.2826226361</v>
+        <v>347438.7846723622</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>2</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>269115.1456473442</v>
+        <v>271294.6476970703</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>344774.924897235</v>
+        <v>346954.4269469612</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>2</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>267350.9734871342</v>
+        <v>269530.4755368604</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>343118.8118121212</v>
+        <v>345298.3138618473</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>2</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0373</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>283541.0458566954</v>
+        <v>285720.5479064216</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>359463.4021277596</v>
+        <v>361642.9041774858</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>2</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>284980.4319511319</v>
+        <v>286675.7496020612</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>363453.5318884568</v>
+        <v>365148.8495393861</v>
       </c>
     </row>
     <row r="36">
@@ -6883,16 +6883,16 @@
         <v>2</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03730104196384632</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>295194.8929320796</v>
+        <v>296648.0863827641</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>375389.7649814264</v>
+        <v>376842.9584321108</v>
       </c>
     </row>
     <row r="38">
@@ -6914,10 +6914,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>7982375.576819404</v>
+        <v>8040737.737115049</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>10311501.09741878</v>
+        <v>10369863.25771442</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1412270.82</v>
+        <v>1404826.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11882329.87374679</v>
+        <v>11874885.49374679</v>
       </c>
     </row>
     <row r="9">

--- a/reports/spark/2026-03/spark_settlement_march_2026.xlsx
+++ b/reports/spark/2026-03/spark_settlement_march_2026.xlsx
@@ -4677,7 +4677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -4896,7 +4896,7 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+          <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
